--- a/client/public/artefactos/ADI-03.xlsx
+++ b/client/public/artefactos/ADI-03.xlsx
@@ -541,7 +541,11 @@
           <t>ADM</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BD SQL Server 2022 en producción; soporta APTEMP02; dominio Plataforma, Seguridad e Interoperabilidad *</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>SQL Server</t>
@@ -584,14 +588,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -604,7 +604,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>YESSENIA IPANAQUE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -614,17 +614,13 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -640,7 +636,11 @@
           <t>AQMV9</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BD SQL Server 2022 en producción; soporta APTEMP02; dominio Plataforma, Seguridad e Interoperabilidad *</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>SQL Server</t>
@@ -683,14 +683,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -703,7 +699,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>YESSENIA IPANAQUE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -713,17 +709,13 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -786,14 +778,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Herramienta/soporte TI *</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -806,7 +794,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>YESSENIA IPANAQUE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -816,17 +804,13 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -842,7 +826,11 @@
           <t>ASDK8</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BD SQL Server 2022 en producción; soporta APTEMP02; dominio Plataforma, Seguridad e Interoperabilidad *</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>SQL Server</t>
@@ -885,14 +873,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -905,7 +889,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>YESSENIA IPANAQUE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -915,17 +899,13 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -988,14 +968,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -1018,12 +994,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1091,14 +1067,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Herramienta/soporte TI *</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -1111,7 +1083,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>YESSENIA IPANAQUE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1121,17 +1093,13 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1194,14 +1162,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Herramienta/soporte TI *</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -1214,7 +1178,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>YESSENIA IPANAQUE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1224,17 +1188,13 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1252,7 +1212,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ficha del Asegurado</t>
+          <t>BD SQL Server 2017 en producción; soporta AP013; dominio Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1297,14 +1257,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -1327,14 +1283,10 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -1400,14 +1352,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -1430,14 +1378,10 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -1458,7 +1402,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ficha del Asegurado</t>
+          <t>BD SQL Server 2017 en producción; soporta AP013; dominio Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1503,14 +1447,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -1533,14 +1473,10 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -1559,7 +1495,11 @@
           <t>BDAUDCEN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Base de datos de auditoría de la plataforma tecnológica, gestionada por OTI</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>Oracle</t>
@@ -1602,38 +1542,30 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Auditoría</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>OTI</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>OTI</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Sin archivado de redo (NOARCHIVELOG). *</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1658,7 +1590,11 @@
           <t>BDAUDIT</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Base de datos de auditoría de la plataforma tecnológica, gestionada por OTI</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>SQL Server</t>
@@ -1666,10 +1602,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Producción</t>
@@ -1677,58 +1617,50 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ONPBDONPPR01</t>
+          <t>ONPSRVPRDSQL17</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COT 5</t>
+          <t>COT 4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>AIX 7.3</t>
+          <t>Windows Server 2019 Standard</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>138644.31</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Auditoría</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>OTI</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>JESUS AGUIRRE</t>
+          <t>OTI</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1736,11 +1668,7 @@
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>No aplica de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1753,7 +1681,11 @@
           <t>BDAUDIT</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Base de datos de auditoría de la plataforma tecnológica, gestionada por OTI</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>SQL Server</t>
@@ -1761,14 +1693,10 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Producción</t>
@@ -1776,66 +1704,58 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ONPSRVPRDSQL17</t>
+          <t>ONPBDONPPR01</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COT 4</t>
+          <t>COT 5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Windows Server 2019 Standard</t>
+          <t>AIX 7.3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>138644.31</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Auditoría</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>OTI</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>OTI</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>No aplica de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1848,7 +1768,11 @@
           <t>BDAUDIT</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Base de datos de auditoría de la plataforma tecnológica, gestionada por OTI</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>SQL Server</t>
@@ -1891,40 +1815,28 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Auditoría</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>OTI</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>OTI</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
@@ -1945,7 +1857,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ficha del Asegurado</t>
+          <t>BD SQL Server 2017 en producción; soporta AP013; dominio Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1990,14 +1902,10 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -2020,14 +1928,10 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -2093,14 +1997,10 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -2113,7 +2013,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESUS AGUIRRE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2123,17 +2023,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Sin archivado de redo (NOARCHIVELOG). *</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2196,14 +2096,10 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Documental y Archivo (Soporte)</t>
@@ -2226,12 +2122,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2254,7 +2150,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ficha del Asegurado</t>
+          <t>BD SQL Server 2017 en producción; soporta AP013; dominio Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2299,14 +2195,10 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -2329,14 +2221,10 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -2402,14 +2290,10 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -2432,14 +2316,10 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -2460,7 +2340,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ficha del Asegurado</t>
+          <t>BD SQL Server 2017 en producción; soporta AP013; dominio Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2505,14 +2385,10 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -2535,14 +2411,10 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -2561,7 +2433,11 @@
           <t>BDONPFP1</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BD Oracle 19.27.0.0.250415 en producción; soporta APTEMP13; dominio Plataforma, Seguridad e Interoperabilidad *</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>Oracle</t>
@@ -2604,14 +2480,10 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -2624,7 +2496,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2634,17 +2506,13 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2660,7 +2528,11 @@
           <t>BDONPFP2</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BD Oracle 19.27.0.0.250415 en producción; soporta APTEMP13; dominio Plataforma, Seguridad e Interoperabilidad *</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>Oracle</t>
@@ -2703,14 +2575,10 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -2723,7 +2591,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2733,17 +2601,13 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2826,7 +2690,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Neol Coras</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2836,17 +2700,13 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2909,12 +2769,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
+          <t>Transaccional (relacional) *</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Documento (1666) · Persona (1527) · Aporte (1493) · Asegurado/Afiliado (1187) · Recaudación/Pago (595) · Inversión/FCR (470) · Pensión/Pensionista (296) · Planilla (237) · Empleador/Aportante (222) · Solicitud (123) · Prestación/Beneficio (92) · Expediente/Trámite (86) · Notificación (41) · Resolución (39) · Beneficiario (38) · Derecho previsional (17) · SCTR (7)</t>
+          <t>Documento (1666) · Persona (1527) · Aporte (1493) · Asegurado/Afiliado (1187) · Recaudación/Pago (595) · Inversión/FCR (470) · Pensión/Pensionista (296) · Planilla (237) · Empleador/Aportante (222) · Solicitud (123) · Prestación/Beneficio (92) · Expediente/Trámite (86) · Notificación (41) · Resolución (39) · Beneficiario (38) · Derecho previsional (17) · SCTR (7) *</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2939,12 +2799,12 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3013,14 +2873,10 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Planillas y pagos (Misional) · Regímenes previsionales (Misional)</t>
@@ -3033,7 +2889,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julio Bautista · Nelly Cardenas · Wendy Hercilla</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3043,17 +2899,13 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -3071,7 +2923,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ficha del Asegurado</t>
+          <t>BD SQL Server 2017 en producción; soporta AP013; dominio Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3116,14 +2968,10 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -3146,14 +2994,10 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -3174,7 +3018,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ficha del Asegurado</t>
+          <t>BD SQL Server 2017 en producción; soporta AP013; dominio Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3219,14 +3063,10 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -3249,14 +3089,10 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -3352,12 +3188,12 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3430,7 +3266,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Documento (555) · Expediente/Trámite (321) · Recaudación/Pago (165) · Pensión/Pensionista (159) · Persona (137) · Beneficiario (45) · Asegurado/Afiliado (30) · Planilla (25) · Empleador/Aportante (19) · Notificación (17)</t>
+          <t>Documento (555) · Expediente/Trámite (321) · Recaudación/Pago (165) · Pensión/Pensionista (159) · Persona (137) · Beneficiario (45) · Asegurado/Afiliado (30) · Planilla (25) · Empleador/Aportante (19) · Notificación (17) *</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3455,12 +3291,12 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3533,7 +3369,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Documento (4629) · Persona (2307) · Planilla (1564) · Expediente/Trámite (1303) · Solicitud (1219) · Pensión/Pensionista (753) · Inversión/FCR (670) · Empleador/Aportante (521) · Recaudación/Pago (250) · Resolución (211) · Asegurado/Afiliado (130) · Aporte (128) · Prestación/Beneficio (115) · Notificación (75) · Beneficiario (56) · Derecho previsional (53) · SCTR (43) · Fiscalización (8)</t>
+          <t>Documento (4629) · Persona (2307) · Planilla (1564) · Expediente/Trámite (1303) · Solicitud (1219) · Pensión/Pensionista (753) · Inversión/FCR (670) · Empleador/Aportante (521) · Recaudación/Pago (250) · Resolución (211) · Asegurado/Afiliado (130) · Aporte (128) · Prestación/Beneficio (115) · Notificación (75) · Beneficiario (56) · Derecho previsional (53) · SCTR (43) · Fiscalización (8) *</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3558,12 +3394,12 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3631,12 +3467,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
+          <t>Transaccional (relacional) *</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Asegurado/Afiliado (641) · Documento (443) · Aporte (346) · Persona (303) · Expediente/Trámite (235) · Recaudación/Pago (187) · Notificación (19) · Pensión/Pensionista (12) · Solicitud (6) · Empleador/Aportante (5)</t>
+          <t>Asegurado/Afiliado (641) · Documento (443) · Aporte (346) · Persona (303) · Expediente/Trámite (235) · Recaudación/Pago (187) · Notificación (19) · Pensión/Pensionista (12) · Solicitud (6) · Empleador/Aportante (5) *</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3661,12 +3497,12 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3764,12 +3600,12 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3837,12 +3673,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
+          <t>Documental/gestión de contenidos *</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Documento (343) · Solicitud (171) · Expediente/Trámite (130) · Notificación (52) · Persona (34) · Beneficiario (14) · Aporte (6)</t>
+          <t>Documento (343) · Solicitud (171) · Expediente/Trámite (130) · Notificación (52) · Persona (34) · Beneficiario (14) · Aporte (6) *</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3867,12 +3703,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -3940,14 +3776,10 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Apelaciones previsionales (Misional) · Gestión Documental y Archivo (Soporte) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -3970,12 +3802,12 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. BD en baja/candidata.</t>
+          <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -4073,12 +3905,12 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. BD en baja/candidata. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. En baja/candidata. *</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -4176,12 +4008,12 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. BD en baja/candidata. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). En baja/candidata. *</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -4254,7 +4086,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Aporte (697) · Asegurado/Afiliado (595) · Documento (541) · Planilla (398) · Persona (381) · Empleador/Aportante (337) · Inversión/FCR (173) · Solicitud (153) · Recaudación/Pago (147) · SCTR (145) · Pensión/Pensionista (136) · Beneficiario (55) · Derecho previsional (21) · Prestación/Beneficio (12) · Notificación (9) · Expediente/Trámite (7)</t>
+          <t>Aporte (697) · Asegurado/Afiliado (595) · Documento (541) · Planilla (398) · Persona (381) · Empleador/Aportante (337) · Inversión/FCR (173) · Solicitud (153) · Recaudación/Pago (147) · SCTR (145) · Pensión/Pensionista (136) · Beneficiario (55) · Derecho previsional (21) · Prestación/Beneficio (12) · Notificación (9) · Expediente/Trámite (7) *</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4279,12 +4111,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4352,14 +4184,10 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -4372,7 +4200,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JORGE VELASQUEZ</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4382,17 +4210,13 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U40" t="inlineStr"/>
@@ -4455,45 +4279,17 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>SANDRA COHAILA</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>Sin aplicacion (consultar al gestor) de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
@@ -4558,14 +4354,10 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -4588,17 +4380,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4665,14 +4457,10 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Analítica/reportería *</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -4685,7 +4473,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4695,17 +4483,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U43" t="inlineStr"/>
@@ -4721,7 +4509,11 @@
           <t>BDPRFNLE</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BD Oracle 11.2.0.3.15 en producción; soporta APTEMP13; dominio Plataforma, Seguridad e Interoperabilidad *</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>Oracle</t>
@@ -4764,14 +4556,10 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Analítica/reportería *</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -4784,7 +4572,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4794,17 +4582,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U44" t="inlineStr"/>
@@ -4872,7 +4660,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Documento (18)</t>
+          <t>Documento (18) *</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4897,12 +4685,12 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. BD en baja/candidata.</t>
+          <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -4973,42 +4761,18 @@
           <t>Base de datos relacional</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>CARLOS SULLON</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Versión fuera de soporte. *</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
           <t>Sin aplicacion consultar al gestor de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
@@ -5073,45 +4837,21 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>CARLOS SULLON</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Versión fuera de soporte. *</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
           <t>Sin aplicacion consultar al gestor de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
@@ -5131,7 +4871,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ficha del Asegurado</t>
+          <t>BD SQL Server 2017 en producción; soporta AP013; dominio Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5176,14 +4916,10 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -5206,14 +4942,10 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -5234,7 +4966,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Servicios_WEB Backend</t>
+          <t>BD SQL Server 2017 en producción; soporta AP092; dominio Plataforma, Seguridad e Interoperabilidad *</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5279,14 +5011,10 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -5299,7 +5027,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>OTI.UIS</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -5309,17 +5037,13 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U49" t="inlineStr"/>
@@ -5337,7 +5061,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ficha del Asegurado</t>
+          <t>BD SQL Server 2017 en producción; soporta AP013, AP091; dominio Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5382,14 +5106,10 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -5412,14 +5132,10 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -5440,7 +5156,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ficha del Asegurado</t>
+          <t>BD SQL Server 2017 en producción; soporta AP013; dominio Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5485,14 +5201,10 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -5515,14 +5227,10 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -5593,7 +5301,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Documento (514) · Recaudación/Pago (353) · Expediente/Trámite (220) · Persona (194) · Notificación (162) · Solicitud (113) · Resolución (45) · Pensión/Pensionista (39) · Apelación (30) · Aporte (18) · Beneficiario (13) · Empleador/Aportante (11)</t>
+          <t>Documento (514) · Recaudación/Pago (353) · Expediente/Trámite (220) · Persona (194) · Notificación (162) · Solicitud (113) · Resolución (45) · Pensión/Pensionista (39) · Apelación (30) · Aporte (18) · Beneficiario (13) · Empleador/Aportante (11) *</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5618,12 +5326,12 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -5691,14 +5399,10 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -5721,14 +5425,10 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -5790,14 +5490,10 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -5810,7 +5506,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5820,17 +5516,13 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U54" t="inlineStr"/>
@@ -5889,14 +5581,10 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -5909,7 +5597,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5919,17 +5607,13 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U55" t="inlineStr"/>
@@ -5988,14 +5672,10 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -6008,7 +5688,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -6018,17 +5698,13 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U56" t="inlineStr"/>
@@ -6087,14 +5763,10 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -6107,7 +5779,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -6117,17 +5789,13 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U57" t="inlineStr"/>
@@ -6186,14 +5854,10 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -6206,7 +5870,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -6216,17 +5880,13 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U58" t="inlineStr"/>
@@ -6285,14 +5945,10 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -6305,7 +5961,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -6315,17 +5971,13 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U59" t="inlineStr"/>
@@ -6388,14 +6040,10 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -6408,7 +6056,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>JHONNY MARTINES</t>
+          <t>JHONNY MARTINEZ</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -6418,17 +6066,13 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U60" t="inlineStr"/>
@@ -6487,14 +6131,10 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Auditoría *</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -6507,7 +6147,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESUS AGUIRRE</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -6517,17 +6157,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U61" t="inlineStr"/>
@@ -6590,12 +6230,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
+          <t>Transaccional (relacional) *</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Recaudación/Pago (756) · Documento (602) · Pensión/Pensionista (577) · Solicitud (327) · Planilla (225) · Beneficiario (169) · Expediente/Trámite (135) · Prestación/Beneficio (98) · Resolución (82) · Persona (78) · Aporte (72) · Derecho previsional (41) · Notificación (25) · SCTR (12) · Asegurado/Afiliado (11) · Fiscalización (7)</t>
+          <t>Recaudación/Pago (756) · Documento (602) · Pensión/Pensionista (577) · Solicitud (327) · Planilla (225) · Beneficiario (169) · Expediente/Trámite (135) · Prestación/Beneficio (98) · Resolución (82) · Persona (78) · Aporte (72) · Derecho previsional (41) · Notificación (25) · SCTR (12) · Asegurado/Afiliado (11) · Fiscalización (7) *</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6610,7 +6250,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Carolina Cordova</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -6620,17 +6260,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Sin archivado de redo (NOARCHIVELOG). Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U62" t="inlineStr"/>
@@ -6693,12 +6333,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
+          <t>Transaccional (relacional) *</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Recaudación/Pago (1234) · Documento (1149) · Pensión/Pensionista (1093) · Beneficiario (763) · Aporte (748) · Solicitud (734) · Prestación/Beneficio (586) · Expediente/Trámite (404) · Persona (368) · Planilla (315) · Derecho previsional (126) · Resolución (122) · Empleador/Aportante (94) · Notificación (39) · Asegurado/Afiliado (17) · SCTR (14) · Fiscalización (7)</t>
+          <t>Recaudación/Pago (1234) · Documento (1149) · Pensión/Pensionista (1093) · Beneficiario (763) · Aporte (748) · Solicitud (734) · Prestación/Beneficio (586) · Expediente/Trámite (404) · Persona (368) · Planilla (315) · Derecho previsional (126) · Resolución (122) · Empleador/Aportante (94) · Notificación (39) · Asegurado/Afiliado (17) · SCTR (14) · Fiscalización (7) *</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6713,7 +6353,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Carolina Cordova</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -6723,17 +6363,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Sin archivado de redo (NOARCHIVELOG). Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U63" t="inlineStr"/>
@@ -6796,12 +6436,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
+          <t>Transaccional (relacional) *</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Recaudación/Pago (2101) · Documento (1157) · Aporte (917) · Pensión/Pensionista (830) · Beneficiario (711) · Solicitud (366) · Expediente/Trámite (366) · Persona (366) · Derecho previsional (329) · Planilla (225) · SCTR (132) · Asegurado/Afiliado (121) · Prestación/Beneficio (96) · Resolución (93) · Notificación (25) · Empleador/Aportante (11) · Fiscalización (7)</t>
+          <t>Recaudación/Pago (2101) · Documento (1157) · Aporte (917) · Pensión/Pensionista (830) · Beneficiario (711) · Solicitud (366) · Expediente/Trámite (366) · Persona (366) · Derecho previsional (329) · Planilla (225) · SCTR (132) · Asegurado/Afiliado (121) · Prestación/Beneficio (96) · Resolución (93) · Notificación (25) · Empleador/Aportante (11) · Fiscalización (7) *</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6816,7 +6456,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Carolina Cordova</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6826,17 +6466,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Sin archivado de redo (NOARCHIVELOG). Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U64" t="inlineStr"/>
@@ -6895,14 +6535,10 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -6925,12 +6561,12 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -6994,14 +6630,10 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -7014,7 +6646,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -7024,17 +6656,13 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U66" t="inlineStr"/>
@@ -7093,40 +6721,16 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
@@ -7192,14 +6796,10 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -7212,7 +6812,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JORGE VELASQUEZ</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -7222,17 +6822,13 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U68" t="inlineStr"/>
@@ -7291,14 +6887,10 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -7311,7 +6903,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -7321,17 +6913,13 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U69" t="inlineStr"/>
@@ -7394,14 +6982,10 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Regímenes previsionales (Misional)</t>
@@ -7424,14 +7008,10 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -7450,7 +7030,11 @@
           <t>GestionNotificaciones</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BD SQL Server 2017 en producción; soporta AP100; dominio Gestión Documental y Archivo *</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>SQL Server</t>
@@ -7493,14 +7077,10 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>Gestión Documental y Archivo (Soporte)</t>
@@ -7513,7 +7093,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Alex aguilar</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -7523,17 +7103,13 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U71" t="inlineStr"/>
@@ -7601,7 +7177,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>SCTR (56)</t>
+          <t>SCTR (56) *</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -7616,7 +7192,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JORGE VELASQUEZ</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -7626,17 +7202,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U72" t="inlineStr"/>
@@ -7652,7 +7228,11 @@
           <t>HangFireJobs</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BD SQL Server 2017 en producción; soporta AP083; dominio Plataforma, Seguridad e Interoperabilidad *</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>SQL Server</t>
@@ -7695,27 +7275,19 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Liz Aquino; Yela Infantes; Julissa Silva; Patricia Vivas; Wendy Hercilla</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -7725,17 +7297,13 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Candidato / De baja *</t>
         </is>
       </c>
       <c r="U73" t="inlineStr"/>
@@ -7798,14 +7366,10 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
@@ -7818,7 +7382,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JORGE VELASQUEZ</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -7828,17 +7392,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. Sin archivado de redo (NOARCHIVELOG). *</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U74" t="inlineStr"/>
@@ -7901,14 +7465,10 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>Apelaciones previsionales (Misional) · Regímenes previsionales (Misional)</t>
@@ -7931,14 +7491,10 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -8004,14 +7560,10 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -8034,12 +7586,12 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -8107,14 +7659,10 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -8137,12 +7685,12 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8210,14 +7758,10 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -8240,12 +7784,12 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8313,14 +7857,10 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -8343,12 +7883,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -8412,14 +7952,10 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -8432,7 +7968,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -8442,17 +7978,13 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U80" t="inlineStr"/>
@@ -8511,14 +8043,10 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -8531,7 +8059,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -8541,17 +8069,13 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U81" t="inlineStr"/>
@@ -8606,40 +8130,16 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
@@ -8701,14 +8201,10 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -8721,7 +8217,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -8731,17 +8227,13 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U83" t="inlineStr"/>
@@ -8834,12 +8326,12 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -8937,12 +8429,12 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -9040,12 +8532,12 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -9109,14 +8601,10 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -9129,7 +8617,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -9139,17 +8627,13 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U87" t="inlineStr"/>
@@ -9217,7 +8701,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Aporte (293) · Persona (167) · Resolución (101) · Documento (77) · Expediente/Trámite (43) · Solicitud (36) · Pensión/Pensionista (26) · Asegurado/Afiliado (23) · Beneficiario (18) · Recaudación/Pago (16) · Empleador/Aportante (6)</t>
+          <t>Aporte (293) · Persona (167) · Resolución (101) · Documento (77) · Expediente/Trámite (43) · Solicitud (36) · Pensión/Pensionista (26) · Asegurado/Afiliado (23) · Beneficiario (18) · Recaudación/Pago (16) · Empleador/Aportante (6) *</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9242,12 +8726,12 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -9315,14 +8799,10 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional) · Seguros previsionales (Misional)</t>
@@ -9345,14 +8825,10 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -9410,14 +8886,10 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -9430,7 +8902,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -9440,17 +8912,13 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U90" t="inlineStr"/>
@@ -9505,14 +8973,10 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -9525,7 +8989,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -9535,17 +8999,13 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U91" t="inlineStr"/>
@@ -9604,14 +9064,10 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -9624,7 +9080,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -9634,17 +9090,13 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U92" t="inlineStr"/>
@@ -9699,14 +9151,10 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -9719,7 +9167,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -9729,17 +9177,13 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U93" t="inlineStr"/>
@@ -9794,14 +9238,10 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -9814,7 +9254,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -9824,17 +9264,13 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U94" t="inlineStr"/>
@@ -9852,7 +9288,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PCSISTEL versión 6</t>
+          <t>BD SQL Server 2019 en producción; soporta APTEMP01; dominio Planeamiento y Gobierno Institucional, Plataforma, Seguridad e Interoperabilidad, Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -9897,14 +9333,10 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Herramienta/soporte TI *</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>Planeamiento y Gobierno Institucional (Estratégico) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -9917,7 +9349,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>UBALDO PONCE</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -9927,17 +9359,13 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U95" t="inlineStr"/>
@@ -10000,14 +9428,10 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Herramienta/soporte TI *</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>Planeamiento y Gobierno Institucional (Estratégico) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -10020,7 +9444,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>UBALDO PONCE</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -10030,17 +9454,13 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U96" t="inlineStr"/>
@@ -10103,14 +9523,10 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Herramienta/soporte TI *</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>Planeamiento y Gobierno Institucional (Estratégico) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -10133,17 +9549,13 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10165,7 +9577,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PCSISTEL versión 8</t>
+          <t>BD SQL Server 2019 en producción; soporta APTEMP01; dominio Planeamiento y Gobierno Institucional, Plataforma, Seguridad e Interoperabilidad, Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -10210,14 +9622,10 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Herramienta/soporte TI *</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>Planeamiento y Gobierno Institucional (Estratégico) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -10230,7 +9638,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>UBALDO PONCE</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -10240,17 +9648,13 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U98" t="inlineStr"/>
@@ -10268,7 +9672,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Histórico de PCSISTEL v8</t>
+          <t>BD SQL Server 2019 en producción; soporta APTEMP01; dominio Planeamiento y Gobierno Institucional, Plataforma, Seguridad e Interoperabilidad, Regímenes previsionales *</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -10313,14 +9717,10 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Herramienta/soporte TI *</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>Planeamiento y Gobierno Institucional (Estratégico) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -10343,17 +9743,13 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -10416,14 +9812,10 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -10436,7 +9828,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -10446,17 +9838,13 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U100" t="inlineStr"/>
@@ -10524,7 +9912,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Notificación (76) · Empleador/Aportante (58) · Expediente/Trámite (7) · Solicitud (5)</t>
+          <t>Notificación (76) · Empleador/Aportante (58) · Expediente/Trámite (7) · Solicitud (5) *</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -10549,12 +9937,12 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. BD en baja/candidata. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). En baja/candidata. *</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
@@ -10652,12 +10040,12 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -10717,14 +10105,10 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -10737,7 +10121,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -10747,17 +10131,13 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U103" t="inlineStr"/>
@@ -10812,14 +10192,10 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -10832,7 +10208,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -10842,17 +10218,13 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Candidato / De baja *</t>
         </is>
       </c>
       <c r="U104" t="inlineStr"/>
@@ -10907,14 +10279,10 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -10927,7 +10295,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -10937,17 +10305,13 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U105" t="inlineStr"/>
@@ -11006,14 +10370,10 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -11026,7 +10386,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -11036,17 +10396,13 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U106" t="inlineStr"/>
@@ -11101,14 +10457,10 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -11121,7 +10473,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -11131,17 +10483,13 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U107" t="inlineStr"/>
@@ -11204,14 +10552,10 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -11234,14 +10578,10 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -11303,14 +10643,10 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -11323,7 +10659,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -11333,17 +10669,13 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U109" t="inlineStr"/>
@@ -11402,40 +10734,16 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
@@ -11497,14 +10805,10 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -11517,7 +10821,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -11527,17 +10831,13 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U111" t="inlineStr"/>
@@ -11600,14 +10900,10 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -11630,14 +10926,10 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -11708,7 +11000,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Documento (397) · Solicitud (46) · Expediente/Trámite (25) · Notificación (13) · Asegurado/Afiliado (7)</t>
+          <t>Documento (397) · Solicitud (46) · Expediente/Trámite (25) · Notificación (13) · Asegurado/Afiliado (7) *</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -11733,12 +11025,12 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -11836,12 +11128,12 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. Contiene datos personales.</t>
+          <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -11905,14 +11197,10 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -11935,12 +11223,12 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -11961,7 +11249,11 @@
           <t>SIGA_1782</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BD SQL Server 2022 en producción; soporta AP101; dominio Gestión Administrativa, Personal y Logística *</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>SQL Server</t>
@@ -12000,14 +11292,10 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -12018,11 +11306,7 @@
           <t>Oficina de Administración</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr">
         <is>
           <t>AP101 SIGA MEF</t>
@@ -12030,17 +11314,13 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Candidato / De baja *</t>
         </is>
       </c>
       <c r="U116" t="inlineStr"/>
@@ -12056,7 +11336,11 @@
           <t>SIGA_55</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>BD SQL Server 2008 R2 en producción; soporta AP101; dominio Gestión Administrativa, Personal y Logística *</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>SQL Server</t>
@@ -12099,14 +11383,10 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -12117,11 +11397,7 @@
           <t>Oficina de Administración</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr">
         <is>
           <t>AP101 SIGA MEF</t>
@@ -12129,17 +11405,17 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Candidato / De baja *</t>
         </is>
       </c>
       <c r="U117" t="inlineStr"/>
@@ -12155,7 +11431,11 @@
           <t>SIGA_55</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>BD SQL Server 2022 en producción; soporta AP101; dominio Gestión Administrativa, Personal y Logística *</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>SQL Server</t>
@@ -12198,14 +11478,10 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -12216,11 +11492,7 @@
           <t>Oficina de Administración</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr">
         <is>
           <t>AP101 SIGA MEF</t>
@@ -12228,14 +11500,10 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
@@ -12301,14 +11569,10 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -12321,7 +11585,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -12331,17 +11595,17 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U119" t="inlineStr"/>
@@ -12404,14 +11668,10 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -12424,7 +11684,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -12434,17 +11694,17 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U120" t="inlineStr"/>
@@ -12507,14 +11767,10 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -12527,7 +11783,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -12537,17 +11793,17 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U121" t="inlineStr"/>
@@ -12610,14 +11866,10 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -12630,7 +11882,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -12640,17 +11892,17 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U122" t="inlineStr"/>
@@ -12713,14 +11965,10 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -12733,7 +11981,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -12743,17 +11991,17 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U123" t="inlineStr"/>
@@ -12816,14 +12064,10 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -12836,7 +12080,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -12846,17 +12090,17 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U124" t="inlineStr"/>
@@ -12919,14 +12163,10 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -12939,7 +12179,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -12949,17 +12189,17 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U125" t="inlineStr"/>
@@ -13022,14 +12262,10 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Integración/consolidación *</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -13042,7 +12278,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -13052,17 +12288,17 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U126" t="inlineStr"/>
@@ -13125,14 +12361,10 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -13145,7 +12377,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -13155,17 +12387,17 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U127" t="inlineStr"/>
@@ -13228,14 +12460,10 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -13248,7 +12476,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -13258,17 +12486,17 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U128" t="inlineStr"/>
@@ -13331,14 +12559,10 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -13351,7 +12575,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -13361,17 +12585,17 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U129" t="inlineStr"/>
@@ -13434,14 +12658,10 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -13454,7 +12674,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -13464,17 +12684,17 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U130" t="inlineStr"/>
@@ -13537,14 +12757,10 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -13557,7 +12773,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -13567,17 +12783,17 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U131" t="inlineStr"/>
@@ -13640,14 +12856,10 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -13660,7 +12872,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -13670,17 +12882,17 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U132" t="inlineStr"/>
@@ -13743,14 +12955,10 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -13763,7 +12971,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -13773,17 +12981,17 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U133" t="inlineStr"/>
@@ -13842,14 +13050,10 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Auditoría *</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
           <t>Integridad, Riesgos y Control Interno (Estratégico)</t>
@@ -13872,14 +13076,10 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr"/>
       <c r="T134" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -13945,14 +13145,10 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -13975,14 +13171,10 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -14048,14 +13240,10 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -14068,7 +13256,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -14078,17 +13266,17 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U136" t="inlineStr"/>
@@ -14151,14 +13339,10 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -14171,7 +13355,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -14181,17 +13365,17 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U137" t="inlineStr"/>
@@ -14254,14 +13438,10 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -14284,14 +13464,10 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -14357,14 +13533,10 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
           <t>Apelaciones previsionales (Misional) · Regímenes previsionales (Misional)</t>
@@ -14387,14 +13559,10 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -14456,14 +13624,10 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -14476,7 +13640,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -14486,17 +13650,13 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U140" t="inlineStr"/>
@@ -14559,14 +13719,10 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -14589,12 +13745,12 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. BD en baja/candidata.</t>
+          <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -14662,14 +13818,10 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -14682,7 +13834,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -14692,17 +13844,17 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U142" t="inlineStr"/>
@@ -14765,14 +13917,10 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -14785,7 +13933,7 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -14795,17 +13943,17 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U143" t="inlineStr"/>
@@ -14868,14 +14016,10 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -14888,7 +14032,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
@@ -14898,17 +14042,17 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U144" t="inlineStr"/>
@@ -14971,14 +14115,10 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -14991,7 +14131,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
@@ -15001,17 +14141,17 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U145" t="inlineStr"/>
@@ -15074,14 +14214,10 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -15094,7 +14230,7 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
@@ -15104,17 +14240,17 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U146" t="inlineStr"/>
@@ -15177,14 +14313,10 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -15197,7 +14329,7 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
@@ -15207,17 +14339,17 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U147" t="inlineStr"/>
@@ -15280,14 +14412,10 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -15300,7 +14428,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
@@ -15310,17 +14438,17 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U148" t="inlineStr"/>
@@ -15383,14 +14511,10 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -15403,7 +14527,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -15413,17 +14537,17 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U149" t="inlineStr"/>
@@ -15486,29 +14610,17 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
           <t>Gestión Documental y Archivo (Soporte)</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
@@ -15516,12 +14628,12 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. BD en baja/candidata.</t>
+          <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
@@ -15589,29 +14701,17 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
           <t>Gestión Documental y Archivo (Soporte)</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
@@ -15619,12 +14719,12 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. BD en baja/candidata.</t>
+          <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
@@ -15692,29 +14792,17 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
           <t>Gestión Documental y Archivo (Soporte)</t>
         </is>
       </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
@@ -15722,12 +14810,12 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. BD en baja/candidata.</t>
+          <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
@@ -15795,29 +14883,17 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
           <t>Gestión Documental y Archivo (Soporte)</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
@@ -15825,12 +14901,12 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. BD en baja/candidata.</t>
+          <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
@@ -15898,29 +14974,17 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
           <t>Gestión Documental y Archivo (Soporte)</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
@@ -15928,12 +14992,12 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción. BD en baja/candidata.</t>
+          <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
@@ -16001,14 +15065,10 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -16021,7 +15081,7 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
@@ -16031,17 +15091,17 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U155" t="inlineStr"/>
@@ -16104,14 +15164,10 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -16134,12 +15190,12 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
@@ -16207,14 +15263,10 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -16227,7 +15279,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
@@ -16237,17 +15289,17 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U157" t="inlineStr"/>
@@ -16310,14 +15362,10 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -16330,7 +15378,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
@@ -16340,17 +15388,17 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U158" t="inlineStr"/>
@@ -16413,14 +15461,10 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -16443,12 +15487,12 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T159" t="inlineStr">
@@ -16516,14 +15560,10 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -16536,7 +15576,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
@@ -16546,17 +15586,17 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U160" t="inlineStr"/>
@@ -16619,14 +15659,10 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -16639,7 +15675,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -16649,17 +15685,17 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U161" t="inlineStr"/>
@@ -16722,14 +15758,10 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -16752,12 +15784,12 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T162" t="inlineStr">
@@ -16825,14 +15857,10 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -16855,12 +15883,12 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T163" t="inlineStr">
@@ -16928,14 +15956,10 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -16948,7 +15972,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -16958,17 +15982,17 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T164" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U164" t="inlineStr"/>
@@ -17031,14 +16055,10 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -17051,7 +16071,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -17061,17 +16081,17 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T165" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U165" t="inlineStr"/>
@@ -17134,14 +16154,10 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -17164,12 +16180,12 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T166" t="inlineStr">
@@ -17237,14 +16253,10 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -17267,12 +16279,12 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
@@ -17340,14 +16352,10 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr">
         <is>
           <t>Seguros previsionales (Misional)</t>
@@ -17370,12 +16378,12 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T168" t="inlineStr">
@@ -17443,14 +16451,10 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -17473,12 +16477,12 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T169" t="inlineStr">
@@ -17546,14 +16550,10 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr">
         <is>
           <t>Acompañamiento al asegurado (Misional)</t>
@@ -17566,7 +16566,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
@@ -17576,17 +16576,17 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alta *</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U170" t="inlineStr"/>
@@ -17649,14 +16649,10 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Documental/gestión de contenidos *</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr">
         <is>
           <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
@@ -17669,7 +16665,7 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -17679,17 +16675,17 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Media *</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>Acceso restringido a producción.</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="T171" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U171" t="inlineStr"/>
@@ -17748,14 +16744,10 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr">
         <is>
           <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
@@ -17768,7 +16760,7 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
@@ -17778,17 +16770,13 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr">
         <is>
-          <t>Pendiente de validar</t>
+          <t>Operativo *</t>
         </is>
       </c>
       <c r="U172" t="inlineStr"/>
@@ -17851,14 +16839,10 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr">
         <is>
           <t>Regímenes previsionales (Misional)</t>
@@ -17881,14 +16865,10 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Alta *</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr">
         <is>
           <t>Operativo</t>
@@ -17950,14 +16930,10 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Transaccional (relacional)</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>Pendiente de validar</t>
-        </is>
-      </c>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr">
         <is>
           <t>Integridad, Riesgos y Control Interno (Estratégico)</t>
@@ -17980,14 +16956,10 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>Acceso restringido a producción.</t>
-        </is>
-      </c>
+          <t>Media *</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr">
         <is>
           <t>Operativo</t>

--- a/client/public/artefactos/ADI-03.xlsx
+++ b/client/public/artefactos/ADI-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U174"/>
+  <dimension ref="A1:W174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,40 +491,50 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Proceso / dominio</t>
+          <t>Tipo(s) de proceso</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>Dominio(s) funcional(es)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Proceso(s) de negocio</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Área usuaria responsable</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Área técnica responsable</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Consumidores</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Aplicaciones consumidoras</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>Relevancia p/ trazabilidad</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Restricciones / limitaciones</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Observaciones de uso actual</t>
         </is>
@@ -594,36 +604,46 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>YESSENIA IPANAQUE</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>APTEMP02 ARANDA</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -689,36 +709,46 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>YESSENIA IPANAQUE</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>APTEMP02 ARANDA</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -784,36 +814,46 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>YESSENIA IPANAQUE</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>APTEMP02 ARANDA</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -879,36 +919,46 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>YESSENIA IPANAQUE</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>APTEMP02 ARANDA</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -974,40 +1024,50 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1073,36 +1133,46 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>YESSENIA IPANAQUE</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>APTEMP02 ARANDA</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1168,36 +1238,46 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>YESSENIA IPANAQUE</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>APTEMP02 ARANDA</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1263,36 +1343,46 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1358,36 +1448,46 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>M4 Reconocimiento de derechos previsionales | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad Funcional de Defensoría del Asegurado</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>AP001 Sistema de Quejas, Sugerencias y Disconformidades del Administrado | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1453,36 +1553,46 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1551,29 +1661,31 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>OTI</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>OTI</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
         <is>
           <t>Sin archivado de redo (NOARCHIVELOG). *</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>No aplica de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
         </is>
@@ -1646,29 +1758,31 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>OTI</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>OTI</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1733,25 +1847,27 @@
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>OTI</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>OTI</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>No aplica de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
         </is>
@@ -1824,25 +1940,27 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>OTI</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>OTI</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1908,36 +2026,46 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2003,40 +2131,50 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>JESUS AGUIRRE</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>APTEMP07 CLOUDCONTROL</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Sin archivado de redo (NOARCHIVELOG). *</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2102,40 +2240,50 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Documental y Archivo (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Documental y Archivo</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Unidad de Gestión Documental</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>AP012 Fedatarios</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2201,36 +2349,46 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2296,36 +2454,46 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>AP015 Home Service</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2391,36 +2559,46 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2486,36 +2664,46 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>CARLOS SULLON</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2581,36 +2769,46 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>CARLOS SULLON</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2680,36 +2878,46 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Neol Coras</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>APTEMP12 REPORTES</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2779,40 +2987,50 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Inversiones previsionales (Misional) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
+          <t>Inversiones previsionales | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>M4 Reconocimiento de derechos previsionales | M9 Administración de inversiones previsionales | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
           <t>Dirección de Inversiones Previsionales · Oficina de Tecnologías de la Información · Subdirección de Finanzas y Estudios Previsionales</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>AP027 Nuevo Sistema de Administración de Inmuebles | AP102 NSCA | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2879,36 +3097,46 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Planillas y pagos (Misional) · Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
+          <t>Planillas y pagos | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | M8 Gestión de planillas</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional · Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>Julio Bautista · Nelly Cardenas · Wendy Hercilla</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>APTEMP11 IMPLEMENTACIÓN DE PROYECTO PAST | APTEMP14 Programa Contigo | APTEMP15 TRANSFERENCIA DE INFORMACION RENIEC</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2974,36 +3202,46 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3069,36 +3307,46 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3168,40 +3416,50 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Inversiones previsionales (Misional) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional) · Seguros previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
+          <t>Inversiones previsionales | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales | Seguros previsionales</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | M3 Acumulación y acreditación de aportes | M4 Reconocimiento de derechos previsionales | M5 Aseguramiento al SCTR | M9 Administración de inversiones previsionales | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Fiscalización Previsional · Subdirección de Inversiones Inmobiliarias · Unidad de Infraestructura y Soporte Tecnológico · Unidad de Ingeniería de Software</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>AP021 Módulo de Afiliación Facultativa | AP022 MAF ONLINE | AP023 Módulo de Consulta de Cuenta Individual del Asegurado al Sistema Nacional de Pensiones | AP034 Portal del SCTR | AP040 Sistema de Gestión SCTR | AP042 Sistema de Administración de Accesos | AP044 Sistema de Administración Inmobiliaria | AP062 Sistema de Parámetros y Mantenimientos Generales | AP063 SRU Registro Unificado DL 20530 | AP083 Sincroniza APP | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3271,40 +3529,50 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
+          <t>Gestión Documental y Archivo | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>M4 Reconocimiento de derechos previsionales | S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
           <t>Ejecutivo/a de Asuntos Procesales · Subdirección de Gestión de Derechos Previsionales · Unidad de Gestión Documental</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>OTI.DE; OTI.AD</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>AP029 NSGA-P | AP030 Nuevo Sistema de Gestión Archivo (Recaudación) | AP041 RCPJ | AP084 Sistema de Tramite Documentario</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3374,40 +3642,50 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte) · Gestión Documental y Archivo (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística | Gestión Documental y Archivo | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>M4 Reconocimiento de derechos previsionales | S2 Gestión de recursos humanos | S3 Gestión del abastecimiento | S4 Gestión documental | S5 Gestión financiera y contable</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
           <t>Oficina de Administración · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Programación y Control Previsional</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>AP043 Sistema de Archivo Central de Planillas | AP057 Sistema Integrado de Gestión Administrativa | AP060 Sistema de Consulta de Stock</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3477,40 +3755,50 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
+          <t>Gestión Documental y Archivo | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | M2 Orientación previsional | M3 Acumulación y acreditación de aportes | S1 Gestión de tecnologías de la información | S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional · Oficina de Tecnologías de la Información · Subdirección de Afiliación y Gestión de Aportes · Unidad de Gestión Documental</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>AP004 AppCodeWeb | AP024 Sistema Módulo de Inscripción Facultativa | AP053 Sistema de Gestión de Archivo Administrativo | AP064 Sistema de Seguimiento y Gestión de los Centros de Atención | AP089 PagoFacultativo - PagoFacil | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3580,40 +3868,50 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte) · Integridad, Riesgos y Control Interno (Estratégico) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Estratégico | Misional | Soporte</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
+          <t>Gestión Documental y Archivo | Integridad, Riesgos y Control Interno | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>E3 Gestión de la integridad y riesgos institucionales | M3 Acumulación y acreditación de aportes | S1 Gestión de tecnologías de la información | S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional · Unidad de Gestión Documental · Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>AP008 Consulta maestro de Datos | AP010 Declaración Jurada Conflicto Intereses | AP055 Sistema de Gestión Documental | AP100 Notificacion Efectiva</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3683,40 +3981,50 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Apelaciones previsionales (Misional) · Gestión Administrativa, Personal y Logística (Soporte) · Gestión Documental y Archivo (Soporte) · Planillas y pagos (Misional) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
+          <t>Apelaciones previsionales | Gestión Administrativa, Personal y Logística | Gestión Documental y Archivo | Planillas y pagos | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | M2 Orientación previsional | M3 Acumulación y acreditación de aportes | M4 Reconocimiento de derechos previsionales | M7 Gestión de apelaciones previsionales | M8 Gestión de planillas | S1 Gestión de tecnologías de la información | S2 Gestión de recursos humanos | S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional · Oficina de Recursos Humanos · Oficina de Tecnologías de la Información · Subdirección de Fiscalización Previsional · Subdirección de Orientación Previsional · Unidad de Gestión Documental</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>AP025 Módulo de Fiscalización | AP061 Sistema del Procedimiento Administrativo Disciplinario S-PAD | AP069 Sistema de VIsualización Documental | AP098 Visualizacion y Carga de contenido | AP099 Notificación Electrónica | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3782,40 +4090,50 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Apelaciones previsionales (Misional) · Gestión Documental y Archivo (Soporte) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
+          <t>Apelaciones previsionales | Gestión Documental y Archivo | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | M2 Orientación previsional | M3 Acumulación y acreditación de aportes | M4 Reconocimiento de derechos previsionales | M7 Gestión de apelaciones previsionales | S1 Gestión de tecnologías de la información | S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional · Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | AP103 AMARA | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Candidato a dar de baja</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3885,40 +4203,50 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte) · Gestión y gobierno de datos previsionales (Misional) · Integridad, Riesgos y Control Interno (Estratégico) · Planillas y pagos (Misional) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Estratégico | Misional | Soporte</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
+          <t>Gestión Documental y Archivo | Gestión y gobierno de datos previsionales | Integridad, Riesgos y Control Interno | Planillas y pagos | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>E3 Gestión de la integridad y riesgos institucionales | M12 Gestión y gobierno de datos previsionales | M2 Orientación previsional | M3 Acumulación y acreditación de aportes | M4 Reconocimiento de derechos previsionales | M8 Gestión de planillas | S1 Gestión de tecnologías de la información | S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
           <t>Oficina de Planeamiento, Presupuesto y Modernización · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Orientación Previsional · Subdirección de Pago de Prestaciones · Unidad de Gestión Documental · Unidad de Infraestructura y Soporte Tecnológico · Unidad de Integridad Institucional y Gestión de Riesgos</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>AP006 Sistema de Autenticación de Usuarios | AP007 Sistema de Gestión de Claves para Instituciones | AP014 Sistema Fonahpu Power Builder | AP035 Sistema de Información ONPVIRTUAL | AP046 Sistema de Consulta de Afiliados al Sistema Privado de Pensiones | AP047 Sistema de Seguimiento de Control Interno | AP048 Sistema de Consulta de Cuenta Individual de Empleadores y Asegurados | AP049 Sistema de Consulta LIBAPO, IMT Y Resoluciones | AP051 Sistema de Seguridad de Accesos | AP052 Sistema Fonahpu Web | AP054 Sistema de Gestión de Control Plantillas | AP056 Sistema de Gestión de documentos APPENS | AP058 Sistema de Recaudación | AP071 Sistema de Servicios Zona Segura ONP | AP088 Sistema de Gestión de Claves virtuales para aportantes y pensionistas</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>DE BAJA</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3988,40 +4316,50 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
+          <t>Gestión Documental y Archivo | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información | S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Gestión Documental · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | AP090 Casilla Electrónica Voluntaria | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). En baja/candidata. *</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Candidato a dar de baja</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4091,40 +4429,50 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Inversiones previsionales (Misional) · Planeamiento y Gobierno Institucional (Estratégico) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Estratégico | Misional | Soporte</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
+          <t>Inversiones previsionales | Planeamiento y Gobierno Institucional | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>E1 Gestión del planeamiento, presupuesto e inversión institucional | M1 Elección e incorporación al régimen previsional | M2 Orientación previsional | M3 Acumulación y acreditación de aportes | M4 Reconocimiento de derechos previsionales | M9 Administración de inversiones previsionales | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
           <t>Dirección de Inversiones Previsionales · Dirección de Regulación Previsional · Oficina de Tecnologías de la Información · Subdirección de Finanzas y Estudios Previsionales</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>AP027 Nuevo Sistema de Administración de Inmuebles | AP036 PIDE | AP045 Sistema de Cálculo Actuarial | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4190,36 +4538,46 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>JORGE VELASQUEZ</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>APTEMP06 JIRA</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4290,7 +4648,9 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr">
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
         <is>
           <t>Sin aplicacion (consultar al gestor) de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
         </is>
@@ -4360,40 +4720,50 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>CARLOS SULLON</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>Sin aplicacion consultar al gestor  de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
         </is>
@@ -4463,40 +4833,50 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>CARLOS SULLON</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4562,40 +4942,50 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>CARLOS SULLON</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4665,40 +5055,50 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>Candidato a dar de baja</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4767,13 +5167,15 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Versión fuera de soporte. *</t>
-        </is>
-      </c>
+      <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
+        <is>
+          <t>Versión fuera de soporte. *</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
         <is>
           <t>Sin aplicacion consultar al gestor de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
         </is>
@@ -4846,13 +5248,15 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>Versión fuera de soporte. *</t>
-        </is>
-      </c>
+      <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
+        <is>
+          <t>Versión fuera de soporte. *</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
         <is>
           <t>Sin aplicacion consultar al gestor de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
         </is>
@@ -4922,36 +5326,46 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5017,36 +5431,46 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
           <t>Unidad de Ingeniería de Software</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>OTI.UIS</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>AP092 Servicios_Web</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5112,36 +5536,46 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | M4 Reconocimiento de derechos previsionales</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes · Unidad Funcional de Defensoría del Asegurado</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>AP013 Ficha del Asegurado | AP091 Disconformidades y Sugerencias</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5207,36 +5641,46 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5306,40 +5750,50 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Complementario (Complementario) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Complementario | Misional | Soporte</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
+          <t>Complementario | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>C5 Asuntos procesales | M2 Orientación previsional | M4 Reconocimiento de derechos previsionales | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
           <t>Ejecutivo/a de Asuntos Procesales · Oficina de Tecnologías de la Información · Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>AP002 Atención de Procesos Judiciales | AP039 Portal Institucional Web de la ONP | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5405,36 +5859,46 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>M2 Orientación previsional</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
           <t>Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>AP093 Tu Zona Segura Back</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5496,36 +5960,46 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5587,36 +6061,46 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5678,36 +6162,46 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5769,36 +6263,46 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5860,36 +6364,46 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5951,36 +6465,46 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6046,36 +6570,46 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>JHONNY MARTINEZ</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>APTEMP04 ARIESCOM</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6137,40 +6671,50 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>JESUS AGUIRRE</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>APTEMP09 AUDITVAULT</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6240,40 +6784,50 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Apelaciones previsionales (Misional) · Planillas y pagos (Misional) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional) · Seguros previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
+          <t>Apelaciones previsionales | Planillas y pagos | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales | Seguros previsionales</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | M4 Reconocimiento de derechos previsionales | M6 Reconocimiento de prestaciones de seguros | M7 Gestión de apelaciones previsionales | M8 Gestión de planillas | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Secretaría Técnica del TAP · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Gestión de Derechos Previsionales · Subdirección de Orientación Previsional · Subdirección de Pago de Prestaciones</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Carolina Cordova</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>AP032 Nuevo Sistema de Pensiones | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Sin archivado de redo (NOARCHIVELOG). Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6343,40 +6897,50 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Apelaciones previsionales (Misional) · Planillas y pagos (Misional) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional) · Seguros previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
+          <t>Apelaciones previsionales | Planillas y pagos | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales | Seguros previsionales</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | M4 Reconocimiento de derechos previsionales | M6 Reconocimiento de prestaciones de seguros | M7 Gestión de apelaciones previsionales | M8 Gestión de planillas | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Secretaría Técnica del TAP · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Gestión de Derechos Previsionales · Subdirección de Orientación Previsional · Subdirección de Pago de Prestaciones</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Carolina Cordova</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>AP032 Nuevo Sistema de Pensiones | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Sin archivado de redo (NOARCHIVELOG). Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6446,40 +7010,50 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Apelaciones previsionales (Misional) · Planillas y pagos (Misional) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional) · Seguros previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
+          <t>Apelaciones previsionales | Planillas y pagos | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales | Seguros previsionales</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | M4 Reconocimiento de derechos previsionales | M6 Reconocimiento de prestaciones de seguros | M7 Gestión de apelaciones previsionales | M8 Gestión de planillas | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Secretaría Técnica del TAP · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Gestión de Derechos Previsionales · Subdirección de Orientación Previsional · Subdirección de Pago de Prestaciones</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Carolina Cordova</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>AP032 Nuevo Sistema de Pensiones | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Sin archivado de redo (NOARCHIVELOG). Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6541,40 +7115,50 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>M4 Reconocimiento de derechos previsionales</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>AP016 Sistema de Consulta de Atención al Cliente INFOBONO (E-SAC)</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6636,36 +7220,46 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6731,12 +7325,14 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr">
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6802,36 +7398,46 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>JORGE VELASQUEZ</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>APTEMP05 ConsultaPersona</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6893,36 +7499,46 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6988,36 +7604,46 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | M2 Orientación previsional</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
           <t>Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>AP059 Sistema de Gestión de Citas y Colas</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7083,36 +7709,46 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
+          <t>Gestión Documental y Archivo</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
           <t>Unidad de Gestión Documental</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>Alex aguilar</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>AP100 Notificacion Efectiva</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7182,40 +7818,50 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>JORGE VELASQUEZ</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>APTEMP10 HARVEST</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="V72" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7281,32 +7927,42 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
+          <t>Soporte</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
           <t>Liz Aquino; Yela Infantes; Julissa Silva; Patricia Vivas; Wendy Hercilla</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>AP083 Sincroniza APP</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
         <is>
           <t>Candidato / De baja *</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7372,40 +8028,50 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>JORGE VELASQUEZ</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>APTEMP08 APP EN OAS</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Sin archivado de redo (NOARCHIVELOG). *</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="V74" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7471,36 +8137,46 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Apelaciones previsionales (Misional) · Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
+          <t>Apelaciones previsionales | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>M2 Orientación previsional | M7 Gestión de apelaciones previsionales</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
           <t>Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>AP019 Landing Page ONP Datos</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7566,40 +8242,50 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7665,40 +8351,50 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="V77" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7764,40 +8460,50 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="V78" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7863,40 +8569,50 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="V79" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7958,36 +8674,46 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8049,36 +8775,46 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8140,12 +8876,14 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr">
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8207,36 +8945,46 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8306,40 +9054,50 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Apelaciones previsionales (Misional) · Planillas y pagos (Misional) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional) · Seguros previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
+          <t>Apelaciones previsionales | Planillas y pagos | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales | Seguros previsionales</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | M4 Reconocimiento de derechos previsionales | M6 Reconocimiento de prestaciones de seguros | M7 Gestión de apelaciones previsionales | M8 Gestión de planillas | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Secretaría Técnica del TAP · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Gestión de Derechos Previsionales · Subdirección de Orientación Previsional · Subdirección de Pago de Prestaciones</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>AP032 Nuevo Sistema de Pensiones | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="V84" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8409,40 +9167,50 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Apelaciones previsionales (Misional) · Planillas y pagos (Misional) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional) · Seguros previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
+          <t>Apelaciones previsionales | Planillas y pagos | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales | Seguros previsionales</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | M4 Reconocimiento de derechos previsionales | M6 Reconocimiento de prestaciones de seguros | M7 Gestión de apelaciones previsionales | M8 Gestión de planillas | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Secretaría Técnica del TAP · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Gestión de Derechos Previsionales · Subdirección de Orientación Previsional · Subdirección de Pago de Prestaciones</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>AP032 Nuevo Sistema de Pensiones | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="V85" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8512,40 +9280,50 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Apelaciones previsionales (Misional) · Planillas y pagos (Misional) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional) · Seguros previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
+          <t>Apelaciones previsionales | Planillas y pagos | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales | Seguros previsionales</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | M4 Reconocimiento de derechos previsionales | M6 Reconocimiento de prestaciones de seguros | M7 Gestión de apelaciones previsionales | M8 Gestión de planillas | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Secretaría Técnica del TAP · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Gestión de Derechos Previsionales · Subdirección de Orientación Previsional · Subdirección de Pago de Prestaciones</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="R86" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>AP032 Nuevo Sistema de Pensiones | AP037 Proyecto Informático de Registro 20530 | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="V86" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8607,36 +9385,46 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr">
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8706,40 +9494,50 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>M4 Reconocimiento de derechos previsionales</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
           <t>Subdirección de Gestión de Derechos Previsionales</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>AP038 Sistema de Consulta de Planillas 20530</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="V88" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8805,36 +9603,46 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional) · Seguros previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
+          <t>Regímenes previsionales | Seguros previsionales</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>M2 Orientación previsional | M6 Reconocimiento de prestaciones de seguros</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
           <t>Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>AP020 Landing Page ONP Virtual</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr">
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8892,36 +9700,46 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr">
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8979,36 +9797,46 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr">
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9070,36 +9898,46 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr">
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9157,36 +9995,46 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr">
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9244,36 +10092,46 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr">
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9339,36 +10197,46 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Planeamiento y Gobierno Institucional (Estratégico) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Estratégico | Misional | Soporte</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
+          <t>Planeamiento y Gobierno Institucional | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>E4 Gestión de la comunicación | M2 Orientación previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="R95" t="inlineStr">
         <is>
           <t>UBALDO PONCE</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>APTEMP01 PCSISTEL</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr">
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9434,36 +10302,46 @@
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Planeamiento y Gobierno Institucional (Estratégico) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Estratégico | Misional | Soporte</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
+          <t>Planeamiento y Gobierno Institucional | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>E4 Gestión de la comunicación | M2 Orientación previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="R96" t="inlineStr">
         <is>
           <t>UBALDO PONCE</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>APTEMP01 PCSISTEL</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="T96" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr">
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9529,36 +10407,46 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Planeamiento y Gobierno Institucional (Estratégico) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Estratégico | Misional | Soporte</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
+          <t>Planeamiento y Gobierno Institucional | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>E4 Gestión de la comunicación | M2 Orientación previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
+      <c r="R97" t="inlineStr">
         <is>
           <t>UBALDO PONCE</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>APTEMP01 PCSISTEL</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr">
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="W97" t="inlineStr">
         <is>
           <t>PCSISTEL - CALL CENTER</t>
         </is>
@@ -9628,36 +10516,46 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Planeamiento y Gobierno Institucional (Estratégico) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Estratégico | Misional | Soporte</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
+          <t>Planeamiento y Gobierno Institucional | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>E4 Gestión de la comunicación | M2 Orientación previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="R98" t="inlineStr">
         <is>
           <t>UBALDO PONCE</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>APTEMP01 PCSISTEL</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="T98" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr">
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9723,36 +10621,46 @@
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Planeamiento y Gobierno Institucional (Estratégico) · Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Estratégico | Misional | Soporte</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
+          <t>Planeamiento y Gobierno Institucional | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>E4 Gestión de la comunicación | M2 Orientación previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="R99" t="inlineStr">
         <is>
           <t>UBALDO PONCE</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>APTEMP01 PCSISTEL</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="T99" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr">
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="W99" t="inlineStr">
         <is>
           <t>PCSISTEL - CALL CENTER</t>
         </is>
@@ -9818,36 +10726,46 @@
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="R100" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr">
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9917,40 +10835,50 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>M4 Reconocimiento de derechos previsionales</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="R101" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr">
+      <c r="S101" t="inlineStr">
         <is>
           <t>AP050 Sistema de Control Plantillas</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr">
+      <c r="T101" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
+      <c r="U101" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). En baja/candidata. *</t>
         </is>
       </c>
-      <c r="T101" t="inlineStr">
+      <c r="V101" t="inlineStr">
         <is>
           <t>Candidato a dar de baja</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10020,40 +10948,50 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
+          <t>Gestión Documental y Archivo | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes · Unidad de Gestión Documental</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
+      <c r="R102" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr">
+      <c r="S102" t="inlineStr">
         <is>
           <t>AP031 Nuevo Sistema de Generación de Plantillas | AP033 Nuevo Sistema de Trámite Documentario</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
+      <c r="T102" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
+      <c r="U102" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="T102" t="inlineStr">
+      <c r="V102" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10111,36 +11049,46 @@
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
+      <c r="R103" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr">
+      <c r="S103" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr">
+      <c r="T103" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr">
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10198,36 +11146,46 @@
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
           <t>Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="R104" t="inlineStr">
         <is>
           <t>Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="T104" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr">
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr">
         <is>
           <t>Candidato / De baja *</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10285,36 +11243,46 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="R105" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="T105" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr">
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr"/>
+      <c r="W105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10376,36 +11344,46 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr">
+      <c r="R106" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr">
+      <c r="S106" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr">
+      <c r="T106" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr">
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10463,36 +11441,46 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr">
+      <c r="R107" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q107" t="inlineStr">
+      <c r="S107" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr">
+      <c r="T107" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr">
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10558,36 +11546,46 @@
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>M2 Orientación previsional</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
           <t>Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr">
+      <c r="R108" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q108" t="inlineStr">
+      <c r="S108" t="inlineStr">
         <is>
           <t>AP018 Landing Page ONP Cultura</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr">
+      <c r="T108" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr">
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10649,36 +11647,46 @@
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr">
+      <c r="R109" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr">
+      <c r="S109" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr">
+      <c r="T109" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr">
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10744,12 +11752,14 @@
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr">
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10811,36 +11821,46 @@
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
+      <c r="R111" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q111" t="inlineStr">
+      <c r="S111" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr">
+      <c r="T111" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr">
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10906,36 +11926,46 @@
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>M2 Orientación previsional</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
           <t>Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr">
+      <c r="R112" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q112" t="inlineStr">
+      <c r="S112" t="inlineStr">
         <is>
           <t>AP018 Landing Page ONP Cultura</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr">
+      <c r="T112" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr">
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11005,40 +12035,50 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
+          <t>Gestión Documental y Archivo</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
+      <c r="R113" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr">
+      <c r="S113" t="inlineStr">
         <is>
           <t>AP026 Nuevo Sistema de Archivo Bonos</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr">
+      <c r="T113" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
+      <c r="U113" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="T113" t="inlineStr">
+      <c r="V113" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11108,40 +12148,50 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Planillas y pagos (Misional) · Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
+          <t>Planillas y pagos | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>M4 Reconocimiento de derechos previsionales | M8 Gestión de planillas</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes · Subdirección de Gestión de Derechos Previsionales · Subdirección de Orientación Previsional · Subdirección de Pago de Prestaciones</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
+      <c r="R114" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr">
+      <c r="S114" t="inlineStr">
         <is>
           <t>AP028 Nuevo Sistema de Bonos de Reconocimiento</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr">
+      <c r="T114" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
+      <c r="U114" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="T114" t="inlineStr">
+      <c r="V114" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11203,40 +12253,50 @@
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>M2 Orientación previsional | M4 Reconocimiento de derechos previsionales | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
           <t>Ejecutivo/a de Asuntos Procesales · Subdirección de Orientación Previsional · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr">
+      <c r="R115" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q115" t="inlineStr">
+      <c r="S115" t="inlineStr">
         <is>
           <t>AP003 ONP Móvil | AP006 Sistema de Autenticación de Usuarios | AP041 RCPJ | AP042 Sistema de Administración de Accesos | AP051 Sistema de Seguridad de Accesos | AP088 Sistema de Gestión de Claves virtuales para aportantes y pensionistas | AP093 Tu Zona Segura Back</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr">
+      <c r="T115" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
+      <c r="U115" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T115" t="inlineStr">
+      <c r="V115" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11298,32 +12358,42 @@
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>S5 Gestión financiera y contable</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
           <t>Oficina de Administración</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr">
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr">
         <is>
           <t>AP101 SIGA MEF</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr">
+      <c r="T116" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr">
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr">
         <is>
           <t>Candidato / De baja *</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11389,36 +12459,46 @@
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>S5 Gestión financiera y contable</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
           <t>Oficina de Administración</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr">
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
         <is>
           <t>AP101 SIGA MEF</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr">
+      <c r="T117" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
+      <c r="U117" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T117" t="inlineStr">
+      <c r="V117" t="inlineStr">
         <is>
           <t>Candidato / De baja *</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11484,32 +12564,42 @@
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>S5 Gestión financiera y contable</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
           <t>Oficina de Administración</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr">
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
         <is>
           <t>AP101 SIGA MEF</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr">
+      <c r="T118" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr">
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11575,40 +12665,50 @@
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr">
+      <c r="R119" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr">
+      <c r="S119" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr">
+      <c r="T119" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
+      <c r="U119" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr">
+      <c r="V119" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11674,40 +12774,50 @@
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr">
+      <c r="R120" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr">
+      <c r="S120" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr">
+      <c r="T120" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
+      <c r="U120" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T120" t="inlineStr">
+      <c r="V120" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11773,40 +12883,50 @@
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr">
+      <c r="R121" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
+      <c r="S121" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr">
+      <c r="T121" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
+      <c r="U121" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T121" t="inlineStr">
+      <c r="V121" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11872,40 +12992,50 @@
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr">
+      <c r="R122" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr">
+      <c r="S122" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr">
+      <c r="T122" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
+      <c r="U122" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T122" t="inlineStr">
+      <c r="V122" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11971,40 +13101,50 @@
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr">
+      <c r="R123" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q123" t="inlineStr">
+      <c r="S123" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr">
+      <c r="T123" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
+      <c r="U123" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T123" t="inlineStr">
+      <c r="V123" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12070,40 +13210,50 @@
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr">
+      <c r="R124" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr">
+      <c r="S124" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr">
+      <c r="T124" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
+      <c r="U124" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T124" t="inlineStr">
+      <c r="V124" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr"/>
+      <c r="W124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12169,40 +13319,50 @@
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr">
+      <c r="R125" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q125" t="inlineStr">
+      <c r="S125" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr">
+      <c r="T125" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
+      <c r="U125" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr">
+      <c r="V125" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12268,40 +13428,50 @@
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr">
+      <c r="R126" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q126" t="inlineStr">
+      <c r="S126" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr">
+      <c r="T126" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
+      <c r="U126" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T126" t="inlineStr">
+      <c r="V126" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr"/>
+      <c r="W126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12367,40 +13537,50 @@
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr">
+      <c r="R127" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr">
+      <c r="S127" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr">
+      <c r="T127" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
+      <c r="U127" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr">
+      <c r="V127" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr"/>
+      <c r="W127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12466,40 +13646,50 @@
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr">
+      <c r="R128" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q128" t="inlineStr">
+      <c r="S128" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr">
+      <c r="T128" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
+      <c r="U128" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr">
+      <c r="V128" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr"/>
+      <c r="W128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12565,40 +13755,50 @@
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P129" t="inlineStr">
+      <c r="R129" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q129" t="inlineStr">
+      <c r="S129" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr">
+      <c r="T129" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
+      <c r="U129" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T129" t="inlineStr">
+      <c r="V129" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr"/>
+      <c r="W129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12664,40 +13864,50 @@
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P130" t="inlineStr">
+      <c r="R130" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q130" t="inlineStr">
+      <c r="S130" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr">
+      <c r="T130" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
+      <c r="U130" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T130" t="inlineStr">
+      <c r="V130" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr"/>
+      <c r="W130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12763,40 +13973,50 @@
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P131" t="inlineStr">
+      <c r="R131" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q131" t="inlineStr">
+      <c r="S131" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr">
+      <c r="T131" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
+      <c r="U131" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T131" t="inlineStr">
+      <c r="V131" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr"/>
+      <c r="W131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12862,40 +14082,50 @@
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr">
+      <c r="R132" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q132" t="inlineStr">
+      <c r="S132" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr">
+      <c r="T132" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
+      <c r="U132" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T132" t="inlineStr">
+      <c r="V132" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr"/>
+      <c r="W132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12961,40 +14191,50 @@
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P133" t="inlineStr">
+      <c r="R133" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q133" t="inlineStr">
+      <c r="S133" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr">
+      <c r="T133" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
+      <c r="U133" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T133" t="inlineStr">
+      <c r="V133" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr"/>
+      <c r="W133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13056,36 +14296,46 @@
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Integridad, Riesgos y Control Interno (Estratégico)</t>
+          <t>Estratégico</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
+          <t>Integridad, Riesgos y Control Interno</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>E3 Gestión de la integridad y riesgos institucionales</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
           <t>Unidad de Integridad Institucional y Gestión de Riesgos</t>
         </is>
       </c>
-      <c r="P134" t="inlineStr">
+      <c r="R134" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q134" t="inlineStr">
+      <c r="S134" t="inlineStr">
         <is>
           <t>AP065 Seguimiento de Observaciones y Recomendaciones de Auditoria</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr">
+      <c r="T134" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr">
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr"/>
+      <c r="W134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13151,36 +14401,46 @@
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>M2 Orientación previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
           <t>Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P135" t="inlineStr">
+      <c r="R135" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q135" t="inlineStr">
+      <c r="S135" t="inlineStr">
         <is>
           <t>AP003 ONP Móvil | AP068 Tu Zona Segura | AP088 Sistema de Gestión de Claves virtuales para aportantes y pensionistas | AP093 Tu Zona Segura Back</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr">
+      <c r="T135" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr"/>
-      <c r="T135" t="inlineStr">
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr"/>
+      <c r="W135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13246,40 +14506,50 @@
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr">
+      <c r="R136" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q136" t="inlineStr">
+      <c r="S136" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr">
+      <c r="T136" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
+      <c r="U136" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T136" t="inlineStr">
+      <c r="V136" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr"/>
+      <c r="W136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13345,40 +14615,50 @@
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional) · Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado | S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
           <t>Dirección de Gestión Previsional</t>
         </is>
       </c>
-      <c r="P137" t="inlineStr">
+      <c r="R137" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q137" t="inlineStr">
+      <c r="S137" t="inlineStr">
         <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr">
+      <c r="T137" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
+      <c r="U137" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T137" t="inlineStr">
+      <c r="V137" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr"/>
+      <c r="W137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13444,36 +14724,46 @@
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>M2 Orientación previsional</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
           <t>Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P138" t="inlineStr">
+      <c r="R138" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q138" t="inlineStr">
+      <c r="S138" t="inlineStr">
         <is>
           <t>AP066 Módulo de Autoservicio Tótem</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr">
+      <c r="T138" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr">
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr"/>
+      <c r="W138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -13539,36 +14829,46 @@
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Apelaciones previsionales (Misional) · Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
+          <t>Apelaciones previsionales | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>M2 Orientación previsional | M7 Gestión de apelaciones previsionales</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
           <t>Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P139" t="inlineStr">
+      <c r="R139" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q139" t="inlineStr">
+      <c r="S139" t="inlineStr">
         <is>
           <t>AP019 Landing Page ONP Datos</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr">
+      <c r="T139" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr"/>
-      <c r="T139" t="inlineStr">
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr"/>
+      <c r="W139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -13630,36 +14930,46 @@
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr">
+      <c r="R140" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q140" t="inlineStr">
+      <c r="S140" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr">
+      <c r="T140" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr"/>
-      <c r="T140" t="inlineStr">
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr"/>
+      <c r="W140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13725,40 +15035,50 @@
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr">
+      <c r="R141" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q141" t="inlineStr">
+      <c r="S141" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr">
+      <c r="T141" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
+      <c r="U141" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="T141" t="inlineStr">
+      <c r="V141" t="inlineStr">
         <is>
           <t>Candidato a dar de baja</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr"/>
+      <c r="W141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13824,40 +15144,50 @@
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr">
+      <c r="R142" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q142" t="inlineStr">
+      <c r="S142" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr">
+      <c r="T142" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
+      <c r="U142" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T142" t="inlineStr">
+      <c r="V142" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr"/>
+      <c r="W142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13923,40 +15253,50 @@
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P143" t="inlineStr">
+      <c r="R143" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q143" t="inlineStr">
+      <c r="S143" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr">
+      <c r="T143" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
+      <c r="U143" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T143" t="inlineStr">
+      <c r="V143" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr"/>
+      <c r="W143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14022,40 +15362,50 @@
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P144" t="inlineStr">
+      <c r="R144" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q144" t="inlineStr">
+      <c r="S144" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R144" t="inlineStr">
+      <c r="T144" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
+      <c r="U144" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T144" t="inlineStr">
+      <c r="V144" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr"/>
+      <c r="W144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14121,40 +15471,50 @@
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P145" t="inlineStr">
+      <c r="R145" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q145" t="inlineStr">
+      <c r="S145" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr">
+      <c r="T145" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
+      <c r="U145" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T145" t="inlineStr">
+      <c r="V145" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr"/>
+      <c r="W145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14220,40 +15580,50 @@
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P146" t="inlineStr">
+      <c r="R146" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q146" t="inlineStr">
+      <c r="S146" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R146" t="inlineStr">
+      <c r="T146" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
+      <c r="U146" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T146" t="inlineStr">
+      <c r="V146" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr"/>
+      <c r="W146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14319,40 +15689,50 @@
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P147" t="inlineStr">
+      <c r="R147" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q147" t="inlineStr">
+      <c r="S147" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R147" t="inlineStr">
+      <c r="T147" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
+      <c r="U147" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T147" t="inlineStr">
+      <c r="V147" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr"/>
+      <c r="W147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14418,40 +15798,50 @@
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P148" t="inlineStr">
+      <c r="R148" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q148" t="inlineStr">
+      <c r="S148" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R148" t="inlineStr">
+      <c r="T148" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
+      <c r="U148" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T148" t="inlineStr">
+      <c r="V148" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr"/>
+      <c r="W148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14517,40 +15907,50 @@
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr">
+      <c r="R149" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q149" t="inlineStr">
+      <c r="S149" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr">
+      <c r="T149" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
+      <c r="U149" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T149" t="inlineStr">
+      <c r="V149" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr"/>
+      <c r="W149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14616,32 +16016,42 @@
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte)</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr">
+          <t>Soporte</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Gestión Documental y Archivo</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
         </is>
       </c>
-      <c r="R150" t="inlineStr">
+      <c r="T150" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
+      <c r="U150" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="T150" t="inlineStr">
+      <c r="V150" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr"/>
+      <c r="W150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14707,32 +16117,42 @@
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte)</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr">
+          <t>Soporte</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Gestión Documental y Archivo</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
         </is>
       </c>
-      <c r="R151" t="inlineStr">
+      <c r="T151" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
+      <c r="U151" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="T151" t="inlineStr">
+      <c r="V151" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr"/>
+      <c r="W151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14798,32 +16218,42 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte)</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr">
+          <t>Soporte</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Gestión Documental y Archivo</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
         </is>
       </c>
-      <c r="R152" t="inlineStr">
+      <c r="T152" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S152" t="inlineStr">
+      <c r="U152" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="T152" t="inlineStr">
+      <c r="V152" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr"/>
+      <c r="W152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14889,32 +16319,42 @@
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte)</t>
-        </is>
-      </c>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr">
+          <t>Soporte</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Gestión Documental y Archivo</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
         </is>
       </c>
-      <c r="R153" t="inlineStr">
+      <c r="T153" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S153" t="inlineStr">
+      <c r="U153" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="T153" t="inlineStr">
+      <c r="V153" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr"/>
+      <c r="W153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14980,32 +16420,42 @@
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
-          <t>Gestión Documental y Archivo (Soporte)</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr">
+          <t>Soporte</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Gestión Documental y Archivo</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>S4 Gestión documental</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
         </is>
       </c>
-      <c r="R154" t="inlineStr">
+      <c r="T154" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S154" t="inlineStr">
+      <c r="U154" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="T154" t="inlineStr">
+      <c r="V154" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr"/>
+      <c r="W154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -15071,40 +16521,50 @@
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P155" t="inlineStr">
+      <c r="R155" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q155" t="inlineStr">
+      <c r="S155" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R155" t="inlineStr">
+      <c r="T155" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S155" t="inlineStr">
+      <c r="U155" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T155" t="inlineStr">
+      <c r="V155" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr"/>
+      <c r="W155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -15170,40 +16630,50 @@
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P156" t="inlineStr">
+      <c r="R156" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q156" t="inlineStr">
+      <c r="S156" t="inlineStr">
         <is>
           <t>AP009 Convocatorias</t>
         </is>
       </c>
-      <c r="R156" t="inlineStr">
+      <c r="T156" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S156" t="inlineStr">
+      <c r="U156" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T156" t="inlineStr">
+      <c r="V156" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr"/>
+      <c r="W156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -15269,40 +16739,50 @@
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr">
+      <c r="R157" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q157" t="inlineStr">
+      <c r="S157" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R157" t="inlineStr">
+      <c r="T157" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S157" t="inlineStr">
+      <c r="U157" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T157" t="inlineStr">
+      <c r="V157" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr"/>
+      <c r="W157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -15368,40 +16848,50 @@
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P158" t="inlineStr">
+      <c r="R158" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q158" t="inlineStr">
+      <c r="S158" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R158" t="inlineStr">
+      <c r="T158" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S158" t="inlineStr">
+      <c r="U158" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T158" t="inlineStr">
+      <c r="V158" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr"/>
+      <c r="W158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -15467,40 +16957,50 @@
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P159" t="inlineStr">
+      <c r="R159" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q159" t="inlineStr">
+      <c r="S159" t="inlineStr">
         <is>
           <t>AP011 Evaluaciones</t>
         </is>
       </c>
-      <c r="R159" t="inlineStr">
+      <c r="T159" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S159" t="inlineStr">
+      <c r="U159" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T159" t="inlineStr">
+      <c r="V159" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr"/>
+      <c r="W159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -15566,40 +17066,50 @@
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P160" t="inlineStr">
+      <c r="R160" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q160" t="inlineStr">
+      <c r="S160" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R160" t="inlineStr">
+      <c r="T160" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S160" t="inlineStr">
+      <c r="U160" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T160" t="inlineStr">
+      <c r="V160" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr"/>
+      <c r="W160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15665,40 +17175,50 @@
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P161" t="inlineStr">
+      <c r="R161" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q161" t="inlineStr">
+      <c r="S161" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R161" t="inlineStr">
+      <c r="T161" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S161" t="inlineStr">
+      <c r="U161" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T161" t="inlineStr">
+      <c r="V161" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr"/>
+      <c r="W161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15764,40 +17284,50 @@
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P162" t="inlineStr">
+      <c r="R162" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q162" t="inlineStr">
+      <c r="S162" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R162" t="inlineStr">
+      <c r="T162" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S162" t="inlineStr">
+      <c r="U162" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T162" t="inlineStr">
+      <c r="V162" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr"/>
+      <c r="W162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -15863,40 +17393,50 @@
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P163" t="inlineStr">
+      <c r="R163" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q163" t="inlineStr">
+      <c r="S163" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R163" t="inlineStr">
+      <c r="T163" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S163" t="inlineStr">
+      <c r="U163" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T163" t="inlineStr">
+      <c r="V163" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr"/>
+      <c r="W163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15962,40 +17502,50 @@
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P164" t="inlineStr">
+      <c r="R164" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q164" t="inlineStr">
+      <c r="S164" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R164" t="inlineStr">
+      <c r="T164" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S164" t="inlineStr">
+      <c r="U164" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T164" t="inlineStr">
+      <c r="V164" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr"/>
+      <c r="W164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -16061,40 +17611,50 @@
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P165" t="inlineStr">
+      <c r="R165" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q165" t="inlineStr">
+      <c r="S165" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R165" t="inlineStr">
+      <c r="T165" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S165" t="inlineStr">
+      <c r="U165" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T165" t="inlineStr">
+      <c r="V165" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr"/>
+      <c r="W165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -16160,40 +17720,50 @@
       <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>M2 Orientación previsional</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
           <t>Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P166" t="inlineStr">
+      <c r="R166" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q166" t="inlineStr">
+      <c r="S166" t="inlineStr">
         <is>
           <t>AP039 Portal Institucional Web de la ONP</t>
         </is>
       </c>
-      <c r="R166" t="inlineStr">
+      <c r="T166" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S166" t="inlineStr">
+      <c r="U166" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T166" t="inlineStr">
+      <c r="V166" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr"/>
+      <c r="W166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -16259,40 +17829,50 @@
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>M2 Orientación previsional</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
           <t>Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P167" t="inlineStr">
+      <c r="R167" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q167" t="inlineStr">
+      <c r="S167" t="inlineStr">
         <is>
           <t>AP039 Portal Institucional Web de la ONP</t>
         </is>
       </c>
-      <c r="R167" t="inlineStr">
+      <c r="T167" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S167" t="inlineStr">
+      <c r="U167" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T167" t="inlineStr">
+      <c r="V167" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr"/>
+      <c r="W167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -16358,40 +17938,50 @@
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr">
         <is>
-          <t>Seguros previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
+          <t>Seguros previsionales</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>M5 Aseguramiento al SCTR</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
           <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
-      <c r="P168" t="inlineStr">
+      <c r="R168" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q168" t="inlineStr">
+      <c r="S168" t="inlineStr">
         <is>
           <t>AP034 Portal del SCTR</t>
         </is>
       </c>
-      <c r="R168" t="inlineStr">
+      <c r="T168" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S168" t="inlineStr">
+      <c r="U168" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T168" t="inlineStr">
+      <c r="V168" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr"/>
+      <c r="W168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -16457,40 +18047,50 @@
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P169" t="inlineStr">
+      <c r="R169" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q169" t="inlineStr">
+      <c r="S169" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R169" t="inlineStr">
+      <c r="T169" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S169" t="inlineStr">
+      <c r="U169" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T169" t="inlineStr">
+      <c r="V169" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr"/>
+      <c r="W169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -16556,40 +18156,50 @@
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr">
         <is>
-          <t>Acompañamiento al asegurado (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
+          <t>Acompañamiento al asegurado</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>M11 Acompañamiento al asegurado</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
           <t>Unidad de Comunicaciones y Relacionamiento</t>
         </is>
       </c>
-      <c r="P170" t="inlineStr">
+      <c r="R170" t="inlineStr">
         <is>
           <t>JESSICA TABACCHI</t>
         </is>
       </c>
-      <c r="Q170" t="inlineStr">
+      <c r="S170" t="inlineStr">
         <is>
           <t>APTEMP16 CASA DEL PENSIONISTA YUYAQ</t>
         </is>
       </c>
-      <c r="R170" t="inlineStr">
+      <c r="T170" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S170" t="inlineStr">
+      <c r="U170" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T170" t="inlineStr">
+      <c r="V170" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr"/>
+      <c r="W170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -16655,40 +18265,50 @@
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística (Soporte)</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
+          <t>Gestión Administrativa, Personal y Logística</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>S2 Gestión de recursos humanos</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
           <t>Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
-      <c r="P171" t="inlineStr">
+      <c r="R171" t="inlineStr">
         <is>
           <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
-      <c r="Q171" t="inlineStr">
+      <c r="S171" t="inlineStr">
         <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="R171" t="inlineStr">
+      <c r="T171" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S171" t="inlineStr">
+      <c r="U171" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="T171" t="inlineStr">
+      <c r="V171" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr"/>
+      <c r="W171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -16750,36 +18370,46 @@
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr">
         <is>
-          <t>Plataforma, Seguridad e Interoperabilidad (Soporte) · Regímenes previsionales (Misional)</t>
+          <t>Misional | Soporte</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
           <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
-      <c r="P172" t="inlineStr">
+      <c r="R172" t="inlineStr">
         <is>
           <t>CARLOS SULLON · Nelly Cardenas</t>
         </is>
       </c>
-      <c r="Q172" t="inlineStr">
+      <c r="S172" t="inlineStr">
         <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="R172" t="inlineStr">
+      <c r="T172" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S172" t="inlineStr"/>
-      <c r="T172" t="inlineStr">
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr">
         <is>
           <t>Operativo *</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr"/>
+      <c r="W172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -16845,36 +18475,46 @@
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr">
         <is>
-          <t>Regímenes previsionales (Misional)</t>
+          <t>Misional</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
+          <t>Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>M2 Orientación previsional</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
           <t>Subdirección de Orientación Previsional</t>
         </is>
       </c>
-      <c r="P173" t="inlineStr">
+      <c r="R173" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q173" t="inlineStr">
+      <c r="S173" t="inlineStr">
         <is>
           <t>AP071 Sistema de Servicios Zona Segura ONP | AP093 Tu Zona Segura Back</t>
         </is>
       </c>
-      <c r="R173" t="inlineStr">
+      <c r="T173" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="S173" t="inlineStr"/>
-      <c r="T173" t="inlineStr">
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr"/>
+      <c r="W173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -16936,36 +18576,46 @@
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr">
         <is>
-          <t>Integridad, Riesgos y Control Interno (Estratégico)</t>
+          <t>Estratégico</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
+          <t>Integridad, Riesgos y Control Interno</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>E3 Gestión de la integridad y riesgos institucionales</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
           <t>Unidad de Integridad Institucional y Gestión de Riesgos</t>
         </is>
       </c>
-      <c r="P174" t="inlineStr">
+      <c r="R174" t="inlineStr">
         <is>
           <t>OTI.DE</t>
         </is>
       </c>
-      <c r="Q174" t="inlineStr">
+      <c r="S174" t="inlineStr">
         <is>
           <t>AP047 Sistema de Seguimiento de Control Interno</t>
         </is>
       </c>
-      <c r="R174" t="inlineStr">
+      <c r="T174" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="S174" t="inlineStr"/>
-      <c r="T174" t="inlineStr">
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr"/>
+      <c r="W174" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/client/public/artefactos/ADI-03.xlsx
+++ b/client/public/artefactos/ADI-03.xlsx
@@ -640,7 +640,7 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
@@ -745,7 +745,7 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
@@ -850,7 +850,7 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
@@ -955,7 +955,7 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -1274,7 +1274,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1714,14 +1714,10 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Producción</t>
@@ -1729,22 +1725,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ONPSRVPRDSQL17</t>
+          <t>ONPBDONPPR01</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COT 4</t>
+          <t>COT 5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Windows Server 2019 Standard</t>
+          <t>AIX 7.3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>138644.31</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1772,17 +1768,17 @@
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Versión fuera de soporte. *</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>No aplica de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1807,10 +1803,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Producción</t>
@@ -1818,22 +1818,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ONPBDONPPR01</t>
+          <t>SRVWNPSDBPR01</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COT 5</t>
+          <t>COT 4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>AIX 7.3</t>
+          <t>Windows Server 2019 Standard</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>138644.31</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1867,11 +1867,7 @@
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No aplica de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
-        </is>
-      </c>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1896,7 +1892,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1911,7 +1907,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SRVWNPSDBPR01</t>
+          <t>ONPSRVPRDSQL17</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1926,7 +1922,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1954,7 +1950,11 @@
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Versión fuera de soporte. *</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
@@ -2914,7 +2914,7 @@
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W25" t="inlineStr"/>
@@ -3133,7 +3133,7 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>DE BAJA</t>
+          <t>De baja</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
@@ -4574,7 +4574,7 @@
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
@@ -5467,7 +5467,7 @@
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W49" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W54" t="inlineStr"/>
@@ -6097,7 +6097,7 @@
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W55" t="inlineStr"/>
@@ -6198,7 +6198,7 @@
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W56" t="inlineStr"/>
@@ -6299,7 +6299,7 @@
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W57" t="inlineStr"/>
@@ -6400,7 +6400,7 @@
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W58" t="inlineStr"/>
@@ -6501,7 +6501,7 @@
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W59" t="inlineStr"/>
@@ -6606,7 +6606,7 @@
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W60" t="inlineStr"/>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W61" t="inlineStr"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W62" t="inlineStr"/>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W63" t="inlineStr"/>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W64" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W66" t="inlineStr"/>
@@ -7434,7 +7434,7 @@
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W68" t="inlineStr"/>
@@ -7535,7 +7535,7 @@
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W69" t="inlineStr"/>
@@ -7745,7 +7745,7 @@
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W71" t="inlineStr"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W72" t="inlineStr"/>
@@ -7956,10 +7956,14 @@
           <t>Media *</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>En baja/candidata. *</t>
+        </is>
+      </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Candidato / De baja *</t>
+          <t>De baja</t>
         </is>
       </c>
       <c r="W73" t="inlineStr"/>
@@ -8068,7 +8072,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W74" t="inlineStr"/>
@@ -8710,7 +8714,7 @@
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W80" t="inlineStr"/>
@@ -8811,7 +8815,7 @@
       <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W81" t="inlineStr"/>
@@ -8981,7 +8985,7 @@
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W83" t="inlineStr"/>
@@ -9421,7 +9425,7 @@
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W87" t="inlineStr"/>
@@ -9736,7 +9740,7 @@
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W90" t="inlineStr"/>
@@ -9833,7 +9837,7 @@
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W91" t="inlineStr"/>
@@ -9934,7 +9938,7 @@
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W92" t="inlineStr"/>
@@ -10031,7 +10035,7 @@
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W93" t="inlineStr"/>
@@ -10128,7 +10132,7 @@
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W94" t="inlineStr"/>
@@ -10233,7 +10237,7 @@
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W95" t="inlineStr"/>
@@ -10338,7 +10342,7 @@
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W96" t="inlineStr"/>
@@ -10443,7 +10447,7 @@
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -10552,7 +10556,7 @@
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W98" t="inlineStr"/>
@@ -10657,7 +10661,7 @@
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -10762,7 +10766,7 @@
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W100" t="inlineStr"/>
@@ -11085,7 +11089,7 @@
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W103" t="inlineStr"/>
@@ -11179,10 +11183,14 @@
           <t>Alta *</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr"/>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>En baja/candidata. *</t>
+        </is>
+      </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>Candidato / De baja *</t>
+          <t>Candidato a dar de baja</t>
         </is>
       </c>
       <c r="W104" t="inlineStr"/>
@@ -11279,7 +11287,7 @@
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W105" t="inlineStr"/>
@@ -11380,7 +11388,7 @@
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W106" t="inlineStr"/>
@@ -11477,7 +11485,7 @@
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W107" t="inlineStr"/>
@@ -11683,7 +11691,7 @@
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W109" t="inlineStr"/>
@@ -11857,7 +11865,7 @@
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W111" t="inlineStr"/>
@@ -12387,10 +12395,14 @@
           <t>Media *</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr"/>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>En baja/candidata. *</t>
+        </is>
+      </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>Candidato / De baja *</t>
+          <t>De baja</t>
         </is>
       </c>
       <c r="W116" t="inlineStr"/>
@@ -12490,12 +12502,12 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>Versión fuera de soporte. *</t>
+          <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>Candidato / De baja *</t>
+          <t>De baja</t>
         </is>
       </c>
       <c r="W117" t="inlineStr"/>
@@ -12705,7 +12717,7 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W119" t="inlineStr"/>
@@ -12814,7 +12826,7 @@
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W120" t="inlineStr"/>
@@ -12923,7 +12935,7 @@
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W121" t="inlineStr"/>
@@ -13032,7 +13044,7 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W122" t="inlineStr"/>
@@ -13141,7 +13153,7 @@
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W123" t="inlineStr"/>
@@ -13250,7 +13262,7 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W124" t="inlineStr"/>
@@ -13359,7 +13371,7 @@
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W125" t="inlineStr"/>
@@ -13468,7 +13480,7 @@
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W126" t="inlineStr"/>
@@ -13577,7 +13589,7 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W127" t="inlineStr"/>
@@ -13686,7 +13698,7 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W128" t="inlineStr"/>
@@ -13795,7 +13807,7 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W129" t="inlineStr"/>
@@ -13904,7 +13916,7 @@
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W130" t="inlineStr"/>
@@ -14013,7 +14025,7 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W131" t="inlineStr"/>
@@ -14122,7 +14134,7 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W132" t="inlineStr"/>
@@ -14231,7 +14243,7 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W133" t="inlineStr"/>
@@ -14546,7 +14558,7 @@
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W136" t="inlineStr"/>
@@ -14655,7 +14667,7 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W137" t="inlineStr"/>
@@ -14966,7 +14978,7 @@
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W140" t="inlineStr"/>
@@ -15184,7 +15196,7 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W142" t="inlineStr"/>
@@ -15293,7 +15305,7 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W143" t="inlineStr"/>
@@ -15402,7 +15414,7 @@
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W144" t="inlineStr"/>
@@ -15511,7 +15523,7 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W145" t="inlineStr"/>
@@ -15620,7 +15632,7 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W146" t="inlineStr"/>
@@ -15729,7 +15741,7 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W147" t="inlineStr"/>
@@ -15838,7 +15850,7 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W148" t="inlineStr"/>
@@ -15947,7 +15959,7 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W149" t="inlineStr"/>
@@ -16561,7 +16573,7 @@
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W155" t="inlineStr"/>
@@ -16779,7 +16791,7 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W157" t="inlineStr"/>
@@ -16888,7 +16900,7 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W158" t="inlineStr"/>
@@ -17106,7 +17118,7 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W160" t="inlineStr"/>
@@ -17215,7 +17227,7 @@
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W161" t="inlineStr"/>
@@ -17542,7 +17554,7 @@
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W164" t="inlineStr"/>
@@ -17651,7 +17663,7 @@
       </c>
       <c r="V165" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W165" t="inlineStr"/>
@@ -18196,7 +18208,7 @@
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W170" t="inlineStr"/>
@@ -18305,7 +18317,7 @@
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W171" t="inlineStr"/>
@@ -18406,7 +18418,7 @@
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>Operativo *</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="W172" t="inlineStr"/>

--- a/client/public/artefactos/ADI-03.xlsx
+++ b/client/public/artefactos/ADI-03.xlsx
@@ -1890,10 +1890,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Producción</t>
@@ -1901,33 +1905,37 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ONPBDONPPR01</t>
+          <t>SRVWNPSDBPR01</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COT 5</t>
+          <t>COT 4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>AIX 7.3</t>
+          <t>Windows Server 2019 Standard</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>138644.31</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1665.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1961,11 +1969,7 @@
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>No aplica de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
-        </is>
-      </c>
+      <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1990,14 +1994,10 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Producción</t>
@@ -2005,37 +2005,33 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SRVWNPSDBPR01</t>
+          <t>ONPBDONPPR01</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COT 4</t>
+          <t>COT 5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Windows Server 2019 Standard</t>
+          <t>AIX 7.3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>138644.31</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1665.67</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2069,7 +2065,11 @@
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>No aplica de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4600,7 +4600,11 @@
           <t>Transaccional (relacional) *</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Modelos y plantillas de documentos, marcas y productos (sistema Aescribe) *</t>
+        </is>
+      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>Misional | Soporte</t>
@@ -5824,7 +5828,11 @@
           <t>Base de datos relacional</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gestión de contenido documental (FileNet GCD) *</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -13929,7 +13937,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BD SQL Server 2008 R2 en producción; soporta AP101; dominio Gestión Administrativa, Personal y Logística *</t>
+          <t>BD SQL Server 2022 en producción; soporta AP101; dominio Gestión Administrativa, Personal y Logística *</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -13939,12 +13947,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2008 R2</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Express</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -13954,7 +13962,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>ONPSRVSMEF</t>
+          <t>SRVWNSMEFPR01</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -13964,12 +13972,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Windows server 2012 R2</t>
+          <t>Windows Server 2022 Standard</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -13979,7 +13987,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>929</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -14024,14 +14032,10 @@
           <t>Media *</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>Versión fuera de soporte. En baja/candidata. *</t>
-        </is>
-      </c>
+      <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>De baja</t>
+          <t>Fuera de alcance</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr"/>
@@ -14049,7 +14053,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BD SQL Server 2022 en producción; soporta AP101; dominio Gestión Administrativa, Personal y Logística *</t>
+          <t>BD SQL Server 2008 R2 en producción; soporta AP101; dominio Gestión Administrativa, Personal y Logística *</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14059,12 +14063,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2008 R2</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Express</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -14074,7 +14078,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>SRVWNSMEFPR01</t>
+          <t>ONPSRVSMEF</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -14084,12 +14088,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Windows Server 2022 Standard</t>
+          <t>Windows server 2012 R2</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -14099,7 +14103,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>938</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -14144,10 +14148,14 @@
           <t>Media *</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr"/>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Versión fuera de soporte. En baja/candidata. *</t>
+        </is>
+      </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>Fuera de alcance</t>
+          <t>De baja</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr"/>

--- a/client/public/artefactos/ADI-03.xlsx
+++ b/client/public/artefactos/ADI-03.xlsx
@@ -3844,17 +3844,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Inversiones previsionales | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales | Seguros previsionales</t>
+          <t>Acompañamiento al asegurado | Gestión Administrativa, Personal y Logística | Inversiones previsionales | Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales | Seguros previsionales</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>M1 Elección e incorporación al régimen previsional | M3 Acumulación y acreditación de aportes | M4 Reconocimiento de derechos previsionales | M5 Aseguramiento al SCTR | M9 Administración de inversiones previsionales | S1 Gestión de tecnologías de la información</t>
+          <t>M1 Elección e incorporación al régimen previsional | M11 Acompañamiento al asegurado | M3 Acumulación y acreditación de aportes | M4 Reconocimiento de derechos previsionales | M5 Aseguramiento al SCTR | M9 Administración de inversiones previsionales | S1 Gestión de tecnologías de la información | S2 Gestión de recursos humanos</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Oficina de Tecnologías de la Información · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Fiscalización Previsional · Subdirección de Inversiones Inmobiliarias · Unidad de Infraestructura y Soporte Tecnológico · Unidad de Ingeniería de Software</t>
+          <t>Dirección de Gestión Previsional · Oficina de Tecnologías de la Información · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Fiscalización Previsional · Subdirección de Inversiones Inmobiliarias · Unidad de Infraestructura y Soporte Tecnológico · Unidad de Ingeniería de Software</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>AP021 Módulo de Afiliación Facultativa | AP022 MAF ONLINE | AP023 Módulo de Consulta de Cuenta Individual del Asegurado al Sistema Nacional de Pensiones | AP034 Portal del SCTR | AP040 Sistema de Gestión SCTR | AP042 Sistema de Administración de Accesos | AP044 Sistema de Administración Inmobiliaria | AP062 Sistema de Parámetros y Mantenimientos Generales | AP063 SRU Registro Unificado DL 20530 | AP083 Sincroniza APP | APTEMP13 Varios</t>
+          <t>AP021 Módulo de Afiliación Facultativa | AP022 MAF ONLINE | AP023 Módulo de Consulta de Cuenta Individual del Asegurado al Sistema Nacional de Pensiones | AP034 Portal del SCTR | AP040 Sistema de Gestión SCTR | AP042 Sistema de Administración de Accesos | AP044 Sistema de Administración Inmobiliaria | AP062 Sistema de Parámetros y Mantenimientos Generales | AP063 SRU Registro Unificado DL 20530 | AP083 Sincroniza APP | APTEMP03 SHAREPOINT | APTEMP13 Varios</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4100,17 +4100,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Gestión Administrativa, Personal y Logística | Gestión Documental y Archivo | Regímenes previsionales</t>
+          <t>Apelaciones previsionales | Gestión Administrativa, Personal y Logística | Gestión Documental y Archivo | Regímenes previsionales</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>M4 Reconocimiento de derechos previsionales | S2 Gestión de recursos humanos | S3 Gestión del abastecimiento | S4 Gestión documental | S5 Gestión financiera y contable</t>
+          <t>M3 Acumulación y acreditación de aportes | M4 Reconocimiento de derechos previsionales | M7 Gestión de apelaciones previsionales | S2 Gestión de recursos humanos | S3 Gestión del abastecimiento | S4 Gestión documental | S5 Gestión financiera y contable</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Oficina de Administración · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Programación y Control Previsional</t>
+          <t>Oficina de Administración · Subdirección de Afiliación y Gestión de Aportes · Subdirección de Orientación Previsional · Subdirección de Programación y Control Previsional</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>AP043 Sistema de Archivo Central de Planillas | AP057 Sistema Integrado de Gestión Administrativa | AP060 Sistema de Consulta de Stock</t>
+          <t xml:space="preserve">AP043 Sistema de Archivo Central de Planillas | AP057 Sistema Integrado de Gestión Administrativa | AP060 Sistema de Consulta de Stock | AP069 Sistema de VIsualización Documental | AP095 </t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>AP006 Sistema de Autenticación de Usuarios | AP007 Sistema de Gestión de Claves para Instituciones | AP014 Sistema Fonahpu Power Builder | AP035 Sistema de Información ONPVIRTUAL | AP046 Sistema de Consulta de Afiliados al Sistema Privado de Pensiones | AP047 Sistema de Seguimiento de Control Interno | AP048 Sistema de Consulta de Cuenta Individual de Empleadores y Asegurados | AP049 Sistema de Consulta LIBAPO, IMT Y Resoluciones | AP051 Sistema de Seguridad de Accesos | AP052 Sistema Fonahpu Web | AP054 Sistema de Gestión de Control Plantillas | AP056 Sistema de Gestión de documentos APPENS | AP058 Sistema de Recaudación | AP071 Sistema de Servicios Zona Segura ONP | AP088 Sistema de Gestión de Claves virtuales para aportantes y pensionistas</t>
+          <t>AP006 Sistema de Autenticación de Usuarios | AP007 Sistema de Gestión de Claves para Instituciones | AP014 Sistema Fonahpu Power Builder | AP035 Sistema de Información ONPVIRTUAL | AP043 Sistema de Archivo Central de Planillas | AP046 Sistema de Consulta de Afiliados al Sistema Privado de Pensiones | AP047 Sistema de Seguimiento de Control Interno | AP048 Sistema de Consulta de Cuenta Individual de Empleadores y Asegurados | AP049 Sistema de Consulta LIBAPO, IMT Y Resoluciones | AP051 Sistema de Seguridad de Accesos | AP052 Sistema Fonahpu Web | AP054 Sistema de Gestión de Control Plantillas | AP056 Sistema de Gestión de documentos APPENS | AP058 Sistema de Recaudación | AP071 Sistema de Servicios Zona Segura ONP | AP088 Sistema de Gestión de Claves virtuales para aportantes y pensionistas</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>AP027 Nuevo Sistema de Administración de Inmuebles | AP036 PIDE | AP045 Sistema de Cálculo Actuarial | APTEMP13 Varios</t>
+          <t>AP027 Nuevo Sistema de Administración de Inmuebles | AP036 PIDE | AP045 Sistema de Cálculo Actuarial | AP097  | APTEMP13 Varios</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">

--- a/client/public/artefactos/ADI-03.xlsx
+++ b/client/public/artefactos/ADI-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z174"/>
+  <dimension ref="A1:AC174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,30 +526,45 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Área técnica responsable</t>
+          <t>Gestor</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Responsable funcional</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>Aplicaciones consumidoras</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>N° integ.</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Integra con (BD / fuentes)</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Relevancia p/ trazabilidad</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Restricciones / limitaciones</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Observaciones de uso actual</t>
         </is>
@@ -659,21 +674,32 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Grupos Resolutores (N1, N2, Analista de Requerimientos, Analista de Activos) Macroservicios asignados por cada responsible</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>APTEMP02 ARANDA</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -779,21 +805,32 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Grupos Resolutores (N1, N2, Analista de Requerimientos, Analista de Activos) Macroservicios asignados por cada responsible</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>APTEMP02 ARANDA</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -899,21 +936,32 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Grupos Resolutores (N1, N2, Analista de Requerimientos, Analista de Activos) Macroservicios asignados por cada responsible</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>APTEMP02 ARANDA</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1019,21 +1067,32 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Grupos Resolutores (N1, N2, Analista de Requerimientos, Analista de Activos) Macroservicios asignados por cada responsible</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>APTEMP02 ARANDA</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1134,30 +1193,41 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1263,21 +1333,32 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Grupos Resolutores (N1, N2, Analista de Requerimientos, Analista de Activos) Macroservicios asignados por cada responsible</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>APTEMP02 ARANDA</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1383,21 +1464,32 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Grupos Resolutores (N1, N2, Analista de Requerimientos, Analista de Activos) Macroservicios asignados por cada responsible</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>APTEMP02 ARANDA</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1498,26 +1590,37 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julio Bautista</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Christian Caro</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1618,26 +1721,37 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | LIZ AQUINO</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Guillermo Benites</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>AP001 Sistema de Quejas, Sugerencias y Disconformidades del Administrado | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr">
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1738,26 +1852,37 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julio Bautista</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Christian Caro</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1844,24 +1969,27 @@
           <t>OTI</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>OTI</t>
-        </is>
-      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>Sin archivado de redo (NOARCHIVELOG). *</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>No aplica de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
         </is>
@@ -1956,20 +2084,23 @@
           <t>OTI</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>OTI</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2054,18 +2185,25 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>OTI</t>
+          <t>JESUS AGUIRRE</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>No aplica de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
         </is>
@@ -2160,24 +2298,27 @@
           <t>OTI</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>OTI</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2278,26 +2419,37 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julio Bautista</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Christian Caro</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr">
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2399,25 +2551,36 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>JESUS AGUIRRE</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>APTEMP07 CLOUDCONTROL</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>Sin archivado de redo (NOARCHIVELOG). *</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2518,30 +2681,41 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Luciana Campos (Locadora - GG.UGD_046) / Nathalie Zuñiga (Ejecutiva de Gestión Documental)</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>AP012 Fedatarios</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2642,26 +2816,37 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julio Bautista</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>Christian Caro</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2762,26 +2947,37 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
+          <t>Ana Pari</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>AP015 Home Service</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2882,26 +3078,37 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julio Bautista</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>Christian Caro</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3005,23 +3212,30 @@
           <t>CARLOS SULLON</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
         <is>
           <t>APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3125,23 +3339,30 @@
           <t>CARLOS SULLON</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
         <is>
           <t>APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3251,21 +3472,32 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
+          <t>JESUS AGUIRRE</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
           <t>APTEMP12 REPORTES</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3370,30 +3602,41 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | Maria Fuentes | Monica Manchego</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
+          <t>Claudia Galeno | Edith Toledo (era la ejecutiva de la Unidad de Finanazas y Estudios actuariales) Actual seria la Sub Dirección de Estudios De Finanzas y Estudios Actuariales</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
           <t>AP027 Nuevo Sistema de Administración de Inmuebles | AP102 NSCA | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3495,26 +3738,37 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Julio Bautista · Nelly Cardenas · Wendy Hercilla</t>
+          <t>Julio Bautista | Nelly Cardenas | Wendy Hercilla</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
+          <t>Chistian Caro / Daniel Talla | Juan Fernández DPG,PP; Pedro Huerta (DPG.SAG) | Luis Gamero</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
           <t>APTEMP11 IMPLEMENTACIÓN DE PROYECTO PAST | APTEMP14 Programa Contigo | APTEMP15 TRANSFERENCIA DE INFORMACION RENIEC</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr">
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3615,26 +3869,37 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julio Bautista</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
+          <t>Christian Caro</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr">
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3735,26 +4000,37 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julio Bautista</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
+          <t>Christian Caro</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr">
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3859,30 +4135,67 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | JESSICA TABACCHI | Jessica Dueñas | Jessica Tabacchi | Liz Aquino | Liz Aquino; Yela Infantes; Julissa Silva; Patricia Vivas; Wendy Hercilla | Patricia Vivas | Yela Infantes</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
+          <t>Anna Garofolin | Claudia Galeno / Juan Vega | Elsa Chuquiano | JOSE VALDÉZ | Liz Aquino Torres | Pedro Huerta | TRANSVERSAL | Wayer Osores</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
           <t>AP021 Módulo de Afiliación Facultativa | AP022 MAF ONLINE | AP023 Módulo de Consulta de Cuenta Individual del Asegurado al Sistema Nacional de Pensiones | AP034 Portal del SCTR | AP040 Sistema de Gestión SCTR | AP042 Sistema de Administración de Accesos | AP044 Sistema de Administración Inmobiliaria | AP062 Sistema de Parámetros y Mantenimientos Generales | AP063 SRU Registro Unificado DL 20530 | AP083 Sincroniza APP | APTEMP03 SHAREPOINT | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>DB Link ← BDPR11G3
+DB Link ← BDPR11G4
+DB Link ← BDPR19G7
+DB Link ← BDPRD11G
+DB Link ← BDPRDBDI
+DB Link ← BDPRDCIA
+DB Link ← PRODNSTD
+DB Link ← SBR2
+DB Link → BDPR11G2
+DB Link → BDPR11G4
+DB Link → BDPR11G5
+DB Link → BDPRD11G
+DB Link → NSP19PRD
+DB Link → PRODNSTD
+DB Link → cadena_pru_gtw
+ETL DataStage ← ?
+ETL DataStage ← INFORMIX
+ETL DataStage ← SUNAT - NOVEDADES
+ETL DataStage ← SUNAT - PADRUC
+ETL DataStage → ?
+ETL DataStage → BDPR11G2
+ETL DataStage → BDPRDBDI
+ETL DataStage → Dataset interno</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3987,30 +4300,50 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>OTI.DE; OTI.AD</t>
+          <t>OTI.UIS | YELA INFANTES | Yela Infantes</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
+          <t>Gustavo Carhuancho | Michael Tafur | Natalye Zuñiga | Walter Chuzon</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
           <t>AP029 NSGA-P | AP030 Nuevo Sistema de Gestión Archivo (Recaudación) | AP041 RCPJ | AP084 Sistema de Tramite Documentario</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>DB Link ← BDPR11G4
+DB Link ← EMI19PRD
+DB Link ← NSP19PRD
+DB Link ← PRODNSTD
+DB Link → BDPR11G2
+DB Link → PRODNSTD</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4115,30 +4448,53 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Liz Aquino | Patricia Vivas | Yela Infantes</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
+          <t>Isabel Valverde | Nelson Palomino | Rosario Sonco / Marco Puente Arnao / Jose Silva / Brandy Zavala / Jenifer Cipra / Liseth Gomez / Mario Ganoza | Victor Silva</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
           <t xml:space="preserve">AP043 Sistema de Archivo Central de Planillas | AP057 Sistema Integrado de Gestión Administrativa | AP060 Sistema de Consulta de Stock | AP069 Sistema de VIsualización Documental | AP095 </t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>DB Link ← BDPR11G2
+DB Link ← BDWWW
+DB Link ← SBR2
+DB Link → BDPR11G2
+DB Link → BDPR11G3
+DB Link → BDPRD11G
+DB Link → NSP18PRD
+DB Link → NSP19PRD
+DB Link → SBR2</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4243,30 +4599,46 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | LIZ AQUINO | Liz Aquino | Patricia Vivas | Sandra Cohaila</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
+          <t>Carlomagno Vasquez | MARIANELA GUTIERREZ | NATALYE ZUÑIGA | Pedro Huerta | Raquel Valencia</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
           <t>AP004 AppCodeWeb | AP024 Sistema Módulo de Inscripción Facultativa | AP053 Sistema de Gestión de Archivo Administrativo | AP064 Sistema de Seguimiento y Gestión de los Centros de Atención | AP089 PagoFacultativo - PagoFacil | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>DB Link ← BDPR11G2
+ETL DataStage ← BDPRDBDI</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4371,30 +4743,47 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Alex aguilar | Nelly Cardenas | OTI.UIS | Yela Infantes</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t>Gerson Yaya | NATALYE ZUÑIGA | Natalye Zuñiga | ORH</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
           <t>AP008 Consulta maestro de Datos | AP010 Declaración Jurada Conflicto Intereses | AP055 Sistema de Gestión Documental | AP100 Notificacion Efectiva</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>DB Link ← BDPRDBDI
+DB Link → BDPR11G2
+DB Link → BDPRDBDI</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4499,30 +4888,41 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Ana Hidalgo | CARLOS SULLON | Liz Aquino | Monica Manchego | Patricia vivas | Ruth Maldonado</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
+          <t>Franck Estela | Gestor no preciso | Isabel Valverde | Natalye Zuñiga | Ruth Maldonado</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
           <t>AP025 Módulo de Fiscalización | AP061 Sistema del Procedimiento Administrativo Disciplinario S-PAD | AP069 Sistema de VIsualización Documental | AP098 Visualizacion y Carga de contenido | AP099 Notificación Electrónica | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4627,30 +5027,41 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
+          <t>EXISTEN VARIOS LIDERES USUARIOS DEPENDIENDO DEL PROCESO | NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | AP103 AMARA | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>Candidato a dar de baja</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4755,30 +5166,65 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Eddie Malca | Jessica Dueñas | Julissa Silva - Jessica Tabacchi | Julissa Silva; Liz Aquino; Yela Infantes; Liz Aquino; Julissa Silva; Wendy Hercilla; Yela Infantes; Luis Castro | Liz Aquino | Liz Aquino; Julissa Silva; Wendy Hercilla; Yela Infantes; Luis Castro | Nelly Cardenas | Yela Infantes</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
+          <t>Ana Hidalgo | Autorización de Descuentos (Jackelin Vidarte) Cálculo Actuarial (Edith Toledo) Migraciones (Luis Alvarado) | David Torres | Edwin Tiburcio Karim Prada | Gerson Yaya | Herta León | Jhon Fernandez / Gerson Yaya | Jose Valdéz | Milko Salas | Nelson Palomino</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
           <t>AP006 Sistema de Autenticación de Usuarios | AP007 Sistema de Gestión de Claves para Instituciones | AP014 Sistema Fonahpu Power Builder | AP035 Sistema de Información ONPVIRTUAL | AP043 Sistema de Archivo Central de Planillas | AP046 Sistema de Consulta de Afiliados al Sistema Privado de Pensiones | AP047 Sistema de Seguimiento de Control Interno | AP048 Sistema de Consulta de Cuenta Individual de Empleadores y Asegurados | AP049 Sistema de Consulta LIBAPO, IMT Y Resoluciones | AP051 Sistema de Seguridad de Accesos | AP052 Sistema Fonahpu Web | AP054 Sistema de Gestión de Control Plantillas | AP056 Sistema de Gestión de documentos APPENS | AP058 Sistema de Recaudación | AP071 Sistema de Servicios Zona Segura ONP | AP088 Sistema de Gestión de Claves virtuales para aportantes y pensionistas</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>DB Link ← BDPR11G2
+DB Link ← BDPR11G4
+DB Link ← BDPRDBDI
+DB Link ← BDPRDCIA
+DB Link ← EMI18PRD
+DB Link ← EMI19PRD
+DB Link ← EMI20PRD
+DB Link ← NSP18PRD
+DB Link ← NSP19PRD
+DB Link ← NSP20PRD
+DB Link ← PLN4
+DB Link ← PRODNSTD
+DB Link ← SBR2
+DB Link → BDPR11G2
+DB Link → BDPRD11G
+DB Link → ESSALUD_REMOTA
+DB Link → NSP18PRD
+DB Link → NSP19PRD
+DB Link → NSP20PRD
+DB Link → PRODNSTD
+DB Link → SBR2</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4883,30 +5329,59 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
+          <t>Julissa Silva | NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | AP090 Casilla Electrónica Voluntaria | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>DB Link ← BDPR19G7
+DB Link → BDPR11G2
+DB Link → BDPR19G7
+DB Link → BDPRD11G
+ETL DataStage ← ?
+ETL DataStage ← BDPR11G2
+ETL DataStage ← RENIEC
+ETL DataStage ← SBR2
+ETL DataStage ← SBS
+ETL DataStage ← SUNAT
+ETL DataStage ← SUNAT - NOVEDADES
+ETL DataStage → ?
+ETL DataStage → Archivo plano
+ETL DataStage → BDPR11G5
+ETL DataStage → BDPRDBDI</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>Candidato a dar de baja</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5011,30 +5486,46 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | Maria Fuentes | Patricia Vivas</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
+          <t>Claudia Galeno | Edith Toledo | Gustavo Carhuancho</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
           <t>AP027 Nuevo Sistema de Administración de Inmuebles | AP036 PIDE | AP045 Sistema de Cálculo Actuarial | AP097  | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>DB Link → BDPR11G2
+DB Link → BDPRD11G</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5140,21 +5631,32 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
+          <t>JORGE VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
           <t>APTEMP06 JIRA</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr">
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5237,12 +5739,23 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SANDRA COHAILA</t>
+        </is>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr">
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr">
         <is>
           <t>Sin aplicacion (consultar al gestor) de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
         </is>
@@ -5350,27 +5863,34 @@
           <t>CARLOS SULLON</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
         <is>
           <t>APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>Sin aplicacion consultar al gestor  de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
         </is>
@@ -5478,27 +5998,34 @@
           <t>CARLOS SULLON</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
         <is>
           <t>APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5602,27 +6129,34 @@
           <t>CARLOS SULLON</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
         <is>
           <t>APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5727,30 +6261,41 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>Candidato a dar de baja</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5837,16 +6382,27 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>CARLOS SULLON</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr">
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr">
         <is>
           <t>Sin aplicacion consultar al gestor de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
         </is>
@@ -5933,16 +6489,27 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>CARLOS SULLON</t>
+        </is>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr">
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr">
         <is>
           <t>Sin aplicacion consultar al gestor de acuerdo al correo: "[ONP-DE_BDI] Solicitud de información pendiente - Inventarios de bases de datos / Cronograma de Reuniones para levantar información" de fecha 14-10-2026 remitido por:Jesus E. Aguirre Daza.</t>
         </is>
@@ -6047,26 +6614,37 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julio Bautista</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
+          <t>Christian Caro</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr">
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6170,23 +6748,30 @@
           <t>OTI.UIS</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
         <is>
           <t>AP092 Servicios_Web</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr">
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6287,26 +6872,37 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julio Bautista | Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
+          <t>Christian Caro | Guillermo Benites</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
           <t>AP013 Ficha del Asegurado | AP091 Disconformidades y Sugerencias</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr">
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6407,26 +7003,37 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julio Bautista</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
+          <t>Christian Caro</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
           <t>AP013 Ficha del Asegurado</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr">
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6531,30 +7138,49 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | Jessica Tabacchi | Yela Infantes</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
+          <t>Herta León | Walter Chuzon</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
           <t>AP002 Atención de Procesos Judiciales | AP039 Portal Institucional Web de la ONP | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>DB Link → BDPR11G4
+DB Link → NSP18PRD
+DB Link → NSP19PRD
+DB Link → NSP20PRD
+DB Link → PRODNSTD</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6655,26 +7281,37 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
+          <t>Herta León</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
           <t>AP093 Tu Zona Segura Back</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr">
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6767,26 +7404,37 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr">
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6879,26 +7527,37 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr">
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6991,26 +7650,37 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr">
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7099,26 +7769,37 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr">
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7211,26 +7892,37 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr">
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7323,26 +8015,37 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr">
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7448,21 +8151,32 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
+          <t>JHONNY MARTINEZ y SERVICIO DE CENTRO DE DATOS (TERCEROS)</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
           <t>APTEMP04 ARIESCOM</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr">
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7552,25 +8266,36 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
+          <t>JESUS AGUIRRE</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
           <t>APTEMP09 AUDITVAULT</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7675,30 +8400,52 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Carolina Cordova</t>
+          <t>CARLOS SULLON | Carolina Cordova</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
+          <t>M4.1 - John Fernandez / Gerson Yaya M4.2 - John Fernandez / Gerson Yaya M4.3 - Gustavo Carhuancho / Ignacio Reyes M6.1 - Alex Sandoval / Ihand Durand M7.1 - Isabel Valverde M8.1 - Edwin Tiburcio / Luis Gamero</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
           <t>AP032 Nuevo Sistema de Pensiones | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>DB Link ← EMI19PRD
+DB Link ← NSP18PRD
+DB Link ← NSP19PRD
+DB Link → BDPRD11G
+DB Link → EMI18PRD
+DB Link → EMI19PRD
+DB Link → NSP18PRD
+DB Link → PRODNSTD</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Sin archivado de redo (NOARCHIVELOG). Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7803,30 +8550,54 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Carolina Cordova</t>
+          <t>CARLOS SULLON | Carolina Cordova</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
+          <t>M4.1 - John Fernandez / Gerson Yaya M4.2 - John Fernandez / Gerson Yaya M4.3 - Gustavo Carhuancho / Ignacio Reyes M6.1 - Alex Sandoval / Ihand Durand M7.1 - Isabel Valverde M8.1 - Edwin Tiburcio / Luis Gamero</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
           <t>AP032 Nuevo Sistema de Pensiones | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>DB Link ← EMI18PRD
+DB Link ← NSP19PRD
+DB Link → BDPR11G3
+DB Link → BDPRD11G
+DB Link → EMI18PRD
+DB Link → EMI19PRD
+DB Link → NSP19PRD
+DB Link → NSP20PRD
+DB Link → PRODNSTD
+DB Link → SBR2</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Sin archivado de redo (NOARCHIVELOG). Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7931,30 +8702,51 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Carolina Cordova</t>
+          <t>CARLOS SULLON | Carolina Cordova</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
+          <t>M4.1 - John Fernandez / Gerson Yaya M4.2 - John Fernandez / Gerson Yaya M4.3 - Gustavo Carhuancho / Ignacio Reyes M6.1 - Alex Sandoval / Ihand Durand M7.1 - Isabel Valverde M8.1 - Edwin Tiburcio / Luis Gamero</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
           <t>AP032 Nuevo Sistema de Pensiones | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>DB Link ← NSP20PRD
+DB Link → BDPRD11G
+DB Link → EMI20PRD
+DB Link → NSP18PRD
+DB Link → NSP19PRD
+DB Link → NSP20PRD
+DB Link → PRODNSTD</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Sin archivado de redo (NOARCHIVELOG). Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8047,30 +8839,41 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Yela Infantes</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
+          <t>Roger Alvear</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
           <t>AP016 Sistema de Consulta de Atención al Cliente INFOBONO (E-SAC)</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8167,26 +8970,37 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr">
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8268,13 +9082,20 @@
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr">
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8380,21 +9201,32 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
+          <t>JORGE VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
           <t>APTEMP05 ConsultaPersona</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr">
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8491,26 +9323,37 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr">
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8611,26 +9454,37 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
+          <t>HERTA LEÓN</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
           <t>AP059 Sistema de Gestión de Citas y Colas</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr">
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8736,21 +9590,32 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
+          <t>NATALYE ZUÑIGA</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
           <t>AP100 Notificacion Efectiva</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr">
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8860,25 +9725,36 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
+          <t>CARLOS SULLON</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
           <t>APTEMP10 HARVEST</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8978,27 +9854,34 @@
           <t>Liz Aquino; Yela Infantes; Julissa Silva; Patricia Vivas; Wendy Hercilla</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
         <is>
           <t>AP083 Sincroniza APP</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9100,25 +9983,36 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
+          <t>JORGE VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
           <t>APTEMP08 APP EN OAS</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Sin archivado de redo (NOARCHIVELOG). *</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9219,26 +10113,37 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
+          <t>Herta León</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
           <t>AP019 Landing Page ONP Datos</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr">
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9339,30 +10244,41 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9463,30 +10379,41 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9587,30 +10514,41 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9711,30 +10649,41 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>JESSICA TABACCHI</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9827,26 +10776,37 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr">
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9939,26 +10899,37 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr">
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10024,13 +10995,20 @@
       <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr">
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10123,26 +11101,37 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr">
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr">
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr"/>
+      <c r="AC83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10247,30 +11236,56 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | Carolina Cordova</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
+          <t>M4.1 - John Fernandez / Gerson Yaya M4.2 - John Fernandez / Gerson Yaya M4.3 - Gustavo Carhuancho / Ignacio Reyes M6.1 - Alex Sandoval / Ihand Durand M7.1 - Isabel Valverde M8.1 - Edwin Tiburcio / Luis Gamero</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
           <t>AP032 Nuevo Sistema de Pensiones | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr">
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>DB Link ← BDPR11G4
+DB Link ← BDPRD11G
+DB Link ← BDWWW
+DB Link ← EMI18PRD
+DB Link ← EMI20PRD
+DB Link ← NSP19PRD
+DB Link ← NSP20PRD
+DB Link ← PRODNSTD
+DB Link → BDPRD11G
+DB Link → EMI18PRD
+DB Link → NSP19PRD
+DB Link → PRODNSTD</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr"/>
+      <c r="AC84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10375,30 +11390,61 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | Carolina Cordova</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
+          <t>M4.1 - John Fernandez / Gerson Yaya M4.2 - John Fernandez / Gerson Yaya M4.3 - Gustavo Carhuancho / Ignacio Reyes M6.1 - Alex Sandoval / Ihand Durand M7.1 - Isabel Valverde M8.1 - Edwin Tiburcio / Luis Gamero</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
           <t>AP032 Nuevo Sistema de Pensiones | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W85" t="inlineStr">
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>DB Link ← BDPR11G2
+DB Link ← BDPR11G4
+DB Link ← BDPRD11G
+DB Link ← BDWWW
+DB Link ← EMI19PRD
+DB Link ← EMI20PRD
+DB Link ← NSP18PRD
+DB Link ← NSP20PRD
+DB Link ← PRODNSTD
+DB Link → BDPR11G3
+DB Link → BDPRD11G
+DB Link → EMI18PRD
+DB Link → EMI19PRD
+DB Link → NSP18PRD
+DB Link → NSP20PRD
+DB Link → PRODNSTD
+DB Link → SBR2</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="AB85" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr"/>
+      <c r="AC85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10503,30 +11549,55 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | Carolina Cordova | Wendy Hercilla</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
+          <t>Gustavo Carhuancho | M4.1 - John Fernandez / Gerson Yaya M4.2 - John Fernandez / Gerson Yaya M4.3 - Gustavo Carhuancho / Ignacio Reyes M6.1 - Alex Sandoval / Ihand Durand M7.1 - Isabel Valverde M8.1 - Edwin Tiburcio / Luis Gamero</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
           <t>AP032 Nuevo Sistema de Pensiones | AP037 Proyecto Informático de Registro 20530 | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>DB Link ← BDPRD11G
+DB Link ← BDWWW
+DB Link ← EMI19PRD
+DB Link ← EMI20PRD
+DB Link ← NSP19PRD
+DB Link ← PRODNSTD
+DB Link → BDPRD11G
+DB Link → EMI20PRD
+DB Link → NSP18PRD
+DB Link → NSP19PRD
+DB Link → PRODNSTD</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="AB86" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr"/>
+      <c r="AC86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10623,26 +11694,37 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr">
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr">
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10747,30 +11829,41 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Wendy Hercilla</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
+          <t>Gustavo Carhuancho</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
           <t>AP038 Sistema de Consulta de Planillas 20530</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr">
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). *</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr"/>
+      <c r="AC88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10871,26 +11964,37 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
+          <t>Herta León</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
           <t>AP020 Landing Page ONP Virtual</t>
         </is>
       </c>
-      <c r="W89" t="inlineStr">
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr">
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr"/>
+      <c r="AC89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10971,26 +12075,37 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr">
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr"/>
+      <c r="AC90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11071,26 +12186,37 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr">
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr">
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr"/>
+      <c r="AC91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11179,26 +12305,37 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W92" t="inlineStr">
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr">
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr"/>
+      <c r="AC92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11279,26 +12416,37 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W93" t="inlineStr">
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr"/>
-      <c r="Y93" t="inlineStr">
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr"/>
+      <c r="AC93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11379,26 +12527,37 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W94" t="inlineStr">
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr"/>
-      <c r="Y94" t="inlineStr">
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr"/>
+      <c r="AC94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11504,21 +12663,32 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
+          <t>Ubaldo Ponce Huachim</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
           <t>APTEMP01 PCSISTEL</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr">
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr">
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr"/>
+      <c r="AC95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11624,21 +12794,32 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
+          <t>Ubaldo Ponce Huachim</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
           <t>APTEMP01 PCSISTEL</t>
         </is>
       </c>
-      <c r="W96" t="inlineStr">
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr">
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr"/>
+      <c r="AC96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11744,21 +12925,32 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
+          <t>Ubaldo Ponce Huachim</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
           <t>APTEMP01 PCSISTEL</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr">
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr">
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AC97" t="inlineStr">
         <is>
           <t>PCSISTEL - CALL CENTER</t>
         </is>
@@ -11868,21 +13060,32 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
+          <t>Ubaldo Ponce Huachim</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
           <t>APTEMP01 PCSISTEL</t>
         </is>
       </c>
-      <c r="W98" t="inlineStr">
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr">
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr"/>
+      <c r="AC98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11988,21 +13191,32 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
+          <t>Ubaldo Ponce Huachim</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
           <t>APTEMP01 PCSISTEL</t>
         </is>
       </c>
-      <c r="W99" t="inlineStr">
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr">
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AC99" t="inlineStr">
         <is>
           <t>PCSISTEL - CALL CENTER</t>
         </is>
@@ -12099,26 +13313,37 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W100" t="inlineStr">
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr">
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr"/>
+      <c r="AC100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12223,30 +13448,48 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Yela Infantes</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
+          <t>Nelson Palomino</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
           <t>AP050 Sistema de Control Plantillas</t>
         </is>
       </c>
-      <c r="W101" t="inlineStr">
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>DB Link ← PRODNSTD
+DB Link → BDPRD11G
+DB Link → PRODNSTD
+DB Link → SBR2</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="AA101" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="AB101" t="inlineStr">
         <is>
           <t>Candidato a dar de baja</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr"/>
+      <c r="AC101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12351,30 +13594,62 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Liz Aquino</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
+          <t>Jhon Fernandez / Gerson Yaya | Roxana Cano Ricardo Gibson Melissa Montenegro Paul Sotelo Gustavo Carhuancho John Fernandez Gerson Yaya</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
           <t>AP031 Nuevo Sistema de Generación de Plantillas | AP033 Nuevo Sistema de Trámite Documentario</t>
         </is>
       </c>
-      <c r="W102" t="inlineStr">
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>DB Link ← BDPR11G2
+DB Link ← BDPR11G3
+DB Link ← BDPRD11G
+DB Link ← BDWWW
+DB Link ← EMI18PRD
+DB Link ← EMI19PRD
+DB Link ← EMI20PRD
+DB Link ← NSP18PRD
+DB Link ← NSP19PRD
+DB Link ← NSP20PRD
+DB Link ← PLN4
+DB Link → BDPR11G2
+DB Link → BDPR11G3
+DB Link → BDPRD11G
+DB Link → NSP18PRD
+DB Link → NSP19PRD
+DB Link → NSP20PRD
+DB Link → PLN4</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X102" t="inlineStr">
+      <c r="AA102" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="AB102" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr"/>
+      <c r="AC102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -12455,26 +13730,37 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W103" t="inlineStr">
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr"/>
-      <c r="Y103" t="inlineStr">
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr"/>
+      <c r="AC103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -12560,25 +13846,36 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento</t>
         </is>
       </c>
-      <c r="W104" t="inlineStr">
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="AA104" t="inlineStr">
         <is>
           <t>En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="AB104" t="inlineStr">
         <is>
           <t>Candidato a dar de baja</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr"/>
+      <c r="AC104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12659,26 +13956,37 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W105" t="inlineStr">
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr"/>
-      <c r="Y105" t="inlineStr">
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr"/>
+      <c r="AC105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -12767,26 +14075,37 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W106" t="inlineStr">
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr"/>
-      <c r="Y106" t="inlineStr">
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr"/>
+      <c r="AC106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -12867,26 +14186,37 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W107" t="inlineStr">
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X107" t="inlineStr"/>
-      <c r="Y107" t="inlineStr">
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr"/>
+      <c r="AC107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -12987,26 +14317,37 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
+          <t>Herta León</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
           <t>AP018 Landing Page ONP Cultura</t>
         </is>
       </c>
-      <c r="W108" t="inlineStr">
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr"/>
-      <c r="Y108" t="inlineStr">
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr"/>
+      <c r="AC108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -13099,26 +14440,37 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W109" t="inlineStr">
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr"/>
-      <c r="Y109" t="inlineStr">
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr"/>
+      <c r="AC109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -13200,13 +14552,20 @@
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr"/>
-      <c r="Y110" t="inlineStr">
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr"/>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr"/>
+      <c r="AC110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13303,26 +14662,37 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W111" t="inlineStr">
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr"/>
-      <c r="Y111" t="inlineStr">
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr"/>
+      <c r="AC111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13423,26 +14793,37 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
+          <t>Herta León</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
           <t>AP018 Landing Page ONP Cultura</t>
         </is>
       </c>
-      <c r="W112" t="inlineStr">
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr"/>
-      <c r="Y112" t="inlineStr">
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr"/>
+      <c r="AC112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -13547,30 +14928,46 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Yela Infantes</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
+          <t>Wilmer Rojas</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
           <t>AP026 Nuevo Sistema de Archivo Bonos</t>
         </is>
       </c>
-      <c r="W113" t="inlineStr">
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>DB Link ← SBR2
+DB Link → SBR2</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
+      <c r="AA113" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="Y113" t="inlineStr">
+      <c r="AB113" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr"/>
+      <c r="AC113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -13675,30 +15072,55 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Yela Infantes</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
+          <t>Melissa Montenegro / Paul Sotelo / Rider Gonzalez / Luz Ayaucan</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
           <t>AP028 Nuevo Sistema de Bonos de Reconocimiento</t>
         </is>
       </c>
-      <c r="W114" t="inlineStr">
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>DB Link ← BDPR11G4
+DB Link ← BDPRD11G
+DB Link ← EMI19PRD
+DB Link ← NSP19PRD
+DB Link ← PLN4
+DB Link ← SAB2
+DB Link → BDPR11G2
+DB Link → BDPR11G4
+DB Link → BDPRD11G
+DB Link → SAB2
+ETL DataStage → BDPRDBDI</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
+      <c r="AA114" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. Datos personales sin cifrado (TDE). Expuesta vía DB links públicos. *</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
+      <c r="AB114" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr"/>
+      <c r="AC114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -13791,30 +15213,41 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>JULISSA SILVA | Julissa Silva - Jessica Tabacchi | Julissa Silva; Liz Aquino; Yela Infantes; Liz Aquino; Julissa Silva; Wendy Hercilla; Yela Infantes; Luis Castro | Liz Aquino | Yela Infantes</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
+          <t>HERTA LEÓN | Herta León | JOSE VALDÉZ | Jose Valdéz | Walter Chuzon</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
           <t>AP003 ONP Móvil | AP006 Sistema de Autenticación de Usuarios | AP041 RCPJ | AP042 Sistema de Administración de Accesos | AP051 Sistema de Seguridad de Accesos | AP088 Sistema de Gestión de Claves virtuales para aportantes y pensionistas | AP093 Tu Zona Segura Back</t>
         </is>
       </c>
-      <c r="W115" t="inlineStr">
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
+      <c r="AA115" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y115" t="inlineStr">
+      <c r="AB115" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr"/>
+      <c r="AC115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -13902,27 +15335,34 @@
         </is>
       </c>
       <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr">
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr">
         <is>
           <t>AP101 SIGA MEF</t>
         </is>
       </c>
-      <c r="W116" t="inlineStr">
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="AA116" t="inlineStr">
         <is>
           <t>En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
+      <c r="AB116" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr"/>
+      <c r="AC116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -14022,23 +15462,30 @@
         </is>
       </c>
       <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr">
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr">
         <is>
           <t>AP101 SIGA MEF</t>
         </is>
       </c>
-      <c r="W117" t="inlineStr">
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr"/>
-      <c r="Y117" t="inlineStr">
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr">
         <is>
           <t>Fuera de alcance</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr"/>
+      <c r="AC117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14138,27 +15585,34 @@
         </is>
       </c>
       <c r="U118" t="inlineStr"/>
-      <c r="V118" t="inlineStr">
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr">
         <is>
           <t>AP101 SIGA MEF</t>
         </is>
       </c>
-      <c r="W118" t="inlineStr">
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
+      <c r="AA118" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="AB118" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr"/>
+      <c r="AC118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -14264,25 +15718,36 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W119" t="inlineStr">
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
+      <c r="AA119" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
+      <c r="AB119" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr"/>
+      <c r="AC119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14388,25 +15853,36 @@
       </c>
       <c r="V120" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W120" t="inlineStr">
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
+      <c r="AA120" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="AB120" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr"/>
+      <c r="AC120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14512,25 +15988,36 @@
       </c>
       <c r="V121" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W121" t="inlineStr">
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X121" t="inlineStr">
+      <c r="AA121" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="AB121" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr"/>
+      <c r="AC121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -14636,25 +16123,36 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W122" t="inlineStr">
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr"/>
+      <c r="Z122" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
+      <c r="AA122" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="AB122" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr"/>
+      <c r="AC122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -14760,25 +16258,36 @@
       </c>
       <c r="V123" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W123" t="inlineStr">
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr"/>
+      <c r="Z123" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X123" t="inlineStr">
+      <c r="AA123" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
+      <c r="AB123" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr"/>
+      <c r="AC123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -14884,25 +16393,36 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W124" t="inlineStr">
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr"/>
+      <c r="Z124" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X124" t="inlineStr">
+      <c r="AA124" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="AB124" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr"/>
+      <c r="AC124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15008,25 +16528,36 @@
       </c>
       <c r="V125" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W125" t="inlineStr">
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
+      <c r="AA125" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
+      <c r="AB125" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr"/>
+      <c r="AC125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -15132,25 +16663,36 @@
       </c>
       <c r="V126" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W126" t="inlineStr">
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
+      <c r="AA126" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y126" t="inlineStr">
+      <c r="AB126" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr"/>
+      <c r="AC126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -15256,25 +16798,36 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W127" t="inlineStr">
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr"/>
+      <c r="Z127" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X127" t="inlineStr">
+      <c r="AA127" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr">
+      <c r="AB127" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr"/>
+      <c r="AC127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -15380,25 +16933,36 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W128" t="inlineStr">
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr"/>
+      <c r="Z128" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X128" t="inlineStr">
+      <c r="AA128" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr">
+      <c r="AB128" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr"/>
+      <c r="AC128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -15504,25 +17068,36 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W129" t="inlineStr">
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X129" t="inlineStr">
+      <c r="AA129" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr">
+      <c r="AB129" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr"/>
+      <c r="AC129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15628,25 +17203,36 @@
       </c>
       <c r="V130" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W130" t="inlineStr">
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr"/>
+      <c r="Z130" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
+      <c r="AA130" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
+      <c r="AB130" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr"/>
+      <c r="AC130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -15752,25 +17338,36 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W131" t="inlineStr">
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X131" t="inlineStr">
+      <c r="AA131" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y131" t="inlineStr">
+      <c r="AB131" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr"/>
+      <c r="AC131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -15876,25 +17473,36 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W132" t="inlineStr">
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr"/>
+      <c r="Z132" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X132" t="inlineStr">
+      <c r="AA132" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y132" t="inlineStr">
+      <c r="AB132" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr"/>
+      <c r="AC132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -16000,25 +17608,36 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W133" t="inlineStr">
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr"/>
+      <c r="Z133" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X133" t="inlineStr">
+      <c r="AA133" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y133" t="inlineStr">
+      <c r="AB133" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr"/>
+      <c r="AC133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -16107,26 +17726,37 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Eddie Malca</t>
         </is>
       </c>
       <c r="V134" t="inlineStr">
         <is>
+          <t>Milko Salas Katia Canales</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
           <t>AP065 Seguimiento de Observaciones y Recomendaciones de Auditoria</t>
         </is>
       </c>
-      <c r="W134" t="inlineStr">
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr"/>
+      <c r="Z134" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr"/>
-      <c r="Y134" t="inlineStr">
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr"/>
+      <c r="AC134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -16227,26 +17857,37 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>JULISSA SILVA | Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
+          <t>HERTA LEÓN | Herta León</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
           <t>AP003 ONP Móvil | AP068 Tu Zona Segura | AP088 Sistema de Gestión de Claves virtuales para aportantes y pensionistas | AP093 Tu Zona Segura Back</t>
         </is>
       </c>
-      <c r="W135" t="inlineStr">
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr"/>
+      <c r="Z135" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X135" t="inlineStr"/>
-      <c r="Y135" t="inlineStr">
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr"/>
+      <c r="AC135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -16352,25 +17993,36 @@
       </c>
       <c r="V136" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W136" t="inlineStr">
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr"/>
+      <c r="Z136" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X136" t="inlineStr">
+      <c r="AA136" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y136" t="inlineStr">
+      <c r="AB136" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr"/>
+      <c r="AC136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -16476,25 +18128,36 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
+          <t>TRANSVERSAL</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
           <t>APTEMP03 SHAREPOINT</t>
         </is>
       </c>
-      <c r="W137" t="inlineStr">
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr"/>
+      <c r="Z137" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X137" t="inlineStr">
+      <c r="AA137" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y137" t="inlineStr">
+      <c r="AB137" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr"/>
+      <c r="AC137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -16595,26 +18258,37 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>MARCO POLO</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
         <is>
+          <t>Roxana Cano</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
           <t>AP066 Módulo de Autoservicio Tótem</t>
         </is>
       </c>
-      <c r="W138" t="inlineStr">
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr"/>
+      <c r="Z138" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X138" t="inlineStr"/>
-      <c r="Y138" t="inlineStr">
+      <c r="AA138" t="inlineStr"/>
+      <c r="AB138" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr"/>
+      <c r="AC138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -16715,26 +18389,37 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
+          <t>Herta León</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
           <t>AP019 Landing Page ONP Datos</t>
         </is>
       </c>
-      <c r="W139" t="inlineStr">
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr"/>
+      <c r="Z139" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X139" t="inlineStr"/>
-      <c r="Y139" t="inlineStr">
+      <c r="AA139" t="inlineStr"/>
+      <c r="AB139" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr"/>
+      <c r="AC139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -16827,26 +18512,37 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W140" t="inlineStr">
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr"/>
+      <c r="Z140" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X140" t="inlineStr"/>
-      <c r="Y140" t="inlineStr">
+      <c r="AA140" t="inlineStr"/>
+      <c r="AB140" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr"/>
+      <c r="AC140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -16947,30 +18643,41 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W141" t="inlineStr">
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr"/>
+      <c r="Z141" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X141" t="inlineStr">
+      <c r="AA141" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y141" t="inlineStr">
+      <c r="AB141" t="inlineStr">
         <is>
           <t>Candidato a dar de baja</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr"/>
+      <c r="AC141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -17076,25 +18783,36 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W142" t="inlineStr">
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X142" t="inlineStr">
+      <c r="AA142" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y142" t="inlineStr">
+      <c r="AB142" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -17200,25 +18918,36 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W143" t="inlineStr">
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr"/>
+      <c r="Z143" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X143" t="inlineStr">
+      <c r="AA143" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y143" t="inlineStr">
+      <c r="AB143" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr"/>
+      <c r="AC143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -17324,25 +19053,36 @@
       </c>
       <c r="V144" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W144" t="inlineStr">
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr"/>
+      <c r="Z144" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X144" t="inlineStr">
+      <c r="AA144" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y144" t="inlineStr">
+      <c r="AB144" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -17448,25 +19188,36 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W145" t="inlineStr">
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr"/>
+      <c r="Z145" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X145" t="inlineStr">
+      <c r="AA145" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y145" t="inlineStr">
+      <c r="AB145" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -17572,25 +19323,36 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W146" t="inlineStr">
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr"/>
+      <c r="Z146" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X146" t="inlineStr">
+      <c r="AA146" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y146" t="inlineStr">
+      <c r="AB146" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr"/>
+      <c r="AC146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -17696,25 +19458,36 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W147" t="inlineStr">
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X147" t="inlineStr">
+      <c r="AA147" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y147" t="inlineStr">
+      <c r="AB147" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr"/>
+      <c r="AC147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -17820,25 +19593,36 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W148" t="inlineStr">
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr"/>
+      <c r="Z148" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X148" t="inlineStr">
+      <c r="AA148" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y148" t="inlineStr">
+      <c r="AB148" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr"/>
+      <c r="AC148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -17944,25 +19728,36 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W149" t="inlineStr">
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr"/>
+      <c r="Z149" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X149" t="inlineStr">
+      <c r="AA149" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr">
+      <c r="AB149" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr"/>
+      <c r="AC149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -18058,27 +19853,34 @@
       </c>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
-      <c r="V150" t="inlineStr">
+      <c r="V150" t="inlineStr"/>
+      <c r="W150" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
         </is>
       </c>
-      <c r="W150" t="inlineStr">
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr"/>
+      <c r="Z150" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X150" t="inlineStr">
+      <c r="AA150" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y150" t="inlineStr">
+      <c r="AB150" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr"/>
+      <c r="AC150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -18174,27 +19976,34 @@
       </c>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
-      <c r="V151" t="inlineStr">
+      <c r="V151" t="inlineStr"/>
+      <c r="W151" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
         </is>
       </c>
-      <c r="W151" t="inlineStr">
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr"/>
+      <c r="Z151" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
+      <c r="AA151" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y151" t="inlineStr">
+      <c r="AB151" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr"/>
+      <c r="AC151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -18290,27 +20099,34 @@
       </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
-      <c r="V152" t="inlineStr">
+      <c r="V152" t="inlineStr"/>
+      <c r="W152" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
         </is>
       </c>
-      <c r="W152" t="inlineStr">
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr"/>
+      <c r="Z152" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X152" t="inlineStr">
+      <c r="AA152" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y152" t="inlineStr">
+      <c r="AB152" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -18406,27 +20222,34 @@
       </c>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
-      <c r="V153" t="inlineStr">
+      <c r="V153" t="inlineStr"/>
+      <c r="W153" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
         </is>
       </c>
-      <c r="W153" t="inlineStr">
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr"/>
+      <c r="Z153" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X153" t="inlineStr">
+      <c r="AA153" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y153" t="inlineStr">
+      <c r="AB153" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -18522,27 +20345,34 @@
       </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
-      <c r="V154" t="inlineStr">
+      <c r="V154" t="inlineStr"/>
+      <c r="W154" t="inlineStr">
         <is>
           <t xml:space="preserve">AP094 </t>
         </is>
       </c>
-      <c r="W154" t="inlineStr">
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr"/>
+      <c r="Z154" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X154" t="inlineStr">
+      <c r="AA154" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. En baja/candidata. *</t>
         </is>
       </c>
-      <c r="Y154" t="inlineStr">
+      <c r="AB154" t="inlineStr">
         <is>
           <t>De baja</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr"/>
+      <c r="AC154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -18648,25 +20478,36 @@
       </c>
       <c r="V155" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W155" t="inlineStr">
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr"/>
+      <c r="Z155" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X155" t="inlineStr">
+      <c r="AA155" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y155" t="inlineStr">
+      <c r="AB155" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr"/>
+      <c r="AC155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -18767,30 +20608,41 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
         <is>
+          <t>Jonathan Ramirez</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
           <t>AP009 Convocatorias</t>
         </is>
       </c>
-      <c r="W156" t="inlineStr">
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr"/>
+      <c r="Z156" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X156" t="inlineStr">
+      <c r="AA156" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y156" t="inlineStr">
+      <c r="AB156" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr"/>
+      <c r="AC156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -18896,25 +20748,36 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W157" t="inlineStr">
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr"/>
+      <c r="Z157" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X157" t="inlineStr">
+      <c r="AA157" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y157" t="inlineStr">
+      <c r="AB157" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr"/>
+      <c r="AC157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -19020,25 +20883,36 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W158" t="inlineStr">
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr"/>
+      <c r="Z158" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X158" t="inlineStr">
+      <c r="AA158" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y158" t="inlineStr">
+      <c r="AB158" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr"/>
+      <c r="AC158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -19139,30 +21013,41 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V159" t="inlineStr">
         <is>
+          <t>Jonathan Ramirez</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
           <t>AP011 Evaluaciones</t>
         </is>
       </c>
-      <c r="W159" t="inlineStr">
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr"/>
+      <c r="Z159" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X159" t="inlineStr">
+      <c r="AA159" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y159" t="inlineStr">
+      <c r="AB159" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr"/>
+      <c r="AC159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -19268,25 +21153,36 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W160" t="inlineStr">
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr"/>
+      <c r="Z160" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X160" t="inlineStr">
+      <c r="AA160" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y160" t="inlineStr">
+      <c r="AB160" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr"/>
+      <c r="AC160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -19392,25 +21288,36 @@
       </c>
       <c r="V161" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W161" t="inlineStr">
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr"/>
+      <c r="Z161" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X161" t="inlineStr">
+      <c r="AA161" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y161" t="inlineStr">
+      <c r="AB161" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr"/>
+      <c r="AC161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -19511,30 +21418,41 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W162" t="inlineStr">
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr"/>
+      <c r="Z162" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X162" t="inlineStr">
+      <c r="AA162" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y162" t="inlineStr">
+      <c r="AB162" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr"/>
+      <c r="AC162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -19635,30 +21553,41 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V163" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W163" t="inlineStr">
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr"/>
+      <c r="Z163" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X163" t="inlineStr">
+      <c r="AA163" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y163" t="inlineStr">
+      <c r="AB163" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr"/>
+      <c r="AC163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -19764,25 +21693,36 @@
       </c>
       <c r="V164" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W164" t="inlineStr">
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr"/>
+      <c r="Z164" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X164" t="inlineStr">
+      <c r="AA164" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y164" t="inlineStr">
+      <c r="AB164" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr"/>
+      <c r="AC164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -19888,25 +21828,36 @@
       </c>
       <c r="V165" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W165" t="inlineStr">
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr"/>
+      <c r="Z165" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X165" t="inlineStr">
+      <c r="AA165" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y165" t="inlineStr">
+      <c r="AB165" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -20007,30 +21958,41 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V166" t="inlineStr">
         <is>
+          <t>Herta León</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
           <t>AP039 Portal Institucional Web de la ONP</t>
         </is>
       </c>
-      <c r="W166" t="inlineStr">
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr"/>
+      <c r="Z166" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X166" t="inlineStr">
+      <c r="AA166" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y166" t="inlineStr">
+      <c r="AB166" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -20131,30 +22093,41 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
         <is>
+          <t>Herta León</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
           <t>AP039 Portal Institucional Web de la ONP</t>
         </is>
       </c>
-      <c r="W167" t="inlineStr">
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr"/>
+      <c r="Z167" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X167" t="inlineStr">
+      <c r="AA167" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y167" t="inlineStr">
+      <c r="AB167" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr"/>
+      <c r="AC167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -20255,30 +22228,41 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V168" t="inlineStr">
         <is>
+          <t>Wayer Osores</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
           <t>AP034 Portal del SCTR</t>
         </is>
       </c>
-      <c r="W168" t="inlineStr">
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr"/>
+      <c r="Z168" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X168" t="inlineStr">
+      <c r="AA168" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y168" t="inlineStr">
+      <c r="AB168" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr"/>
+      <c r="AC168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -20379,30 +22363,41 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W169" t="inlineStr">
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr"/>
+      <c r="Z169" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X169" t="inlineStr">
+      <c r="AA169" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y169" t="inlineStr">
+      <c r="AB169" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -20508,25 +22503,36 @@
       </c>
       <c r="V170" t="inlineStr">
         <is>
+          <t>KARINA MENDOZA</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
           <t>APTEMP16 CASA DEL PENSIONISTA YUYAQ</t>
         </is>
       </c>
-      <c r="W170" t="inlineStr">
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr"/>
+      <c r="Z170" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X170" t="inlineStr">
+      <c r="AA170" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y170" t="inlineStr">
+      <c r="AB170" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -20632,25 +22638,36 @@
       </c>
       <c r="V171" t="inlineStr">
         <is>
+          <t>Angie Surco</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
           <t>AP017 Intranet ONP - ORBI</t>
         </is>
       </c>
-      <c r="W171" t="inlineStr">
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr"/>
+      <c r="Z171" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X171" t="inlineStr">
+      <c r="AA171" t="inlineStr">
         <is>
           <t>Versión fuera de soporte. *</t>
         </is>
       </c>
-      <c r="Y171" t="inlineStr">
+      <c r="AB171" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr"/>
+      <c r="AC171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -20747,26 +22764,37 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>CARLOS SULLON · Nelly Cardenas</t>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
         <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
           <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
         </is>
       </c>
-      <c r="W172" t="inlineStr">
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr"/>
+      <c r="Z172" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X172" t="inlineStr"/>
-      <c r="Y172" t="inlineStr">
+      <c r="AA172" t="inlineStr"/>
+      <c r="AB172" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr"/>
+      <c r="AC172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -20867,26 +22895,37 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Julissa Silva - Jessica Tabacchi</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
         <is>
+          <t>Herta León</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
           <t>AP071 Sistema de Servicios Zona Segura ONP | AP093 Tu Zona Segura Back</t>
         </is>
       </c>
-      <c r="W173" t="inlineStr">
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr"/>
+      <c r="Z173" t="inlineStr">
         <is>
           <t>Alta *</t>
         </is>
       </c>
-      <c r="X173" t="inlineStr"/>
-      <c r="Y173" t="inlineStr">
+      <c r="AA173" t="inlineStr"/>
+      <c r="AB173" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr"/>
+      <c r="AC173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -20975,26 +23014,37 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>OTI.DE</t>
+          <t>Eddie Malca</t>
         </is>
       </c>
       <c r="V174" t="inlineStr">
         <is>
+          <t>Milko Salas</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
           <t>AP047 Sistema de Seguimiento de Control Interno</t>
         </is>
       </c>
-      <c r="W174" t="inlineStr">
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr"/>
+      <c r="Z174" t="inlineStr">
         <is>
           <t>Media *</t>
         </is>
       </c>
-      <c r="X174" t="inlineStr"/>
-      <c r="Y174" t="inlineStr">
+      <c r="AA174" t="inlineStr"/>
+      <c r="AB174" t="inlineStr">
         <is>
           <t>Operativo</t>
         </is>
       </c>
-      <c r="Z174" t="inlineStr"/>
+      <c r="AC174" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/client/public/artefactos/ADI-03.xlsx
+++ b/client/public/artefactos/ADI-03.xlsx
@@ -4167,9 +4167,9 @@
 DB Link → BDPR11G4
 DB Link → BDPR11G5
 DB Link → BDPRD11G
+DB Link → INFORMIX
 DB Link → NSP19PRD
 DB Link → PRODNSTD
-DB Link → cadena_pru_gtw
 ETL DataStage ← ?
 ETL DataStage ← INFORMIX
 ETL DataStage ← SUNAT - NOVEDADES

--- a/client/public/artefactos/ADI-03.xlsx
+++ b/client/public/artefactos/ADI-03.xlsx
@@ -8909,7 +8909,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ONPBMONDBP01</t>
+          <t>ONPWPSDBP01</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8948,56 +8948,24 @@
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Misional | Soporte</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>CARLOS SULLON | Nelly Cardenas</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>NELLY CARDENAS</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>Alta *</t>
-        </is>
-      </c>
+      <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr"/>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Operativo</t>
+          <t>Fuera de alcance</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9036,7 +9004,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ONPWPSDBP01</t>
+          <t>ONPBMONDBP01</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -9075,24 +9043,56 @@
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Misional | Soporte</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
+        </is>
+      </c>
       <c r="X67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Alta *</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Fuera de alcance</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>v10.5.0.4</t>
+          <t>v9.5.0.9</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -10965,22 +10965,34 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ONPBMDBP01</t>
+          <t>ONPBMONDBP01</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>COT 4</t>
+          <t>COT 5</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>AIX 7.2</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
+          <t>AIX 6.1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
@@ -10988,24 +11000,56 @@
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Misional | Soporte</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
+        </is>
+      </c>
       <c r="X82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>Alta *</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>Fuera de alcance</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -11033,7 +11077,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>v9.5.0.9</t>
+          <t>v10.5.0.4</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -11044,34 +11088,22 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ONPBMONDBP01</t>
+          <t>ONPBMDBP01</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>COT 5</t>
+          <t>COT 4</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>AIX 6.1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
+          <t>AIX 7.2</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
@@ -11079,56 +11111,24 @@
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Misional | Soporte</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>CARLOS SULLON | Nelly Cardenas</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>NELLY CARDENAS</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
-        </is>
-      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>Alta *</t>
-        </is>
-      </c>
+      <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>Operativo</t>
+          <t>Fuera de alcance</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>v10.1.0.5</t>
+          <t>v10.5.0.8</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ONPODMCBDP01</t>
+          <t>ONPODMSBDP01</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>453.46</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -14531,38 +14531,70 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Transaccional (relacional) *</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Misional | Soporte</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>CARLOS SULLON | Nelly Cardenas</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>NELLY CARDENAS</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>Transaccional (relacional) *</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
-      <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Y110" t="inlineStr"/>
-      <c r="Z110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>Alta *</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr"/>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>Fuera de alcance</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -14590,7 +14622,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>v10.5.0.8</t>
+          <t>v10.1.0.5</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -14601,7 +14633,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>ONPODMSBDP01</t>
+          <t>ONPODMCBDP01</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -14616,7 +14648,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>453.46</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -14626,12 +14658,12 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>235</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -14640,56 +14672,24 @@
         </is>
       </c>
       <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>Misional | Soporte</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>Plataforma, Seguridad e Interoperabilidad | Regímenes previsionales</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>M1 Elección e incorporación al régimen previsional | S1 Gestión de tecnologías de la información</t>
-        </is>
-      </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>Oficina de Tecnologías de la Información · Unidad de Infraestructura y Soporte Tecnológico</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>CARLOS SULLON | Nelly Cardenas</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>NELLY CARDENAS</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>AP005 Sistema de Aportes y Pensionamiento | APTEMP13 Varios</t>
-        </is>
-      </c>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr"/>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>Alta *</t>
-        </is>
-      </c>
+      <c r="Z111" t="inlineStr"/>
       <c r="AA111" t="inlineStr"/>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>Operativo</t>
+          <t>Fuera de alcance</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BD SQL Server 2022 en producción; soporta AP101; dominio Gestión Administrativa, Personal y Logística *</t>
+          <t>BD SQL Server 2022 en producción; soporta AP057; dominio Gestión Administrativa, Personal y Logística *</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>S5 Gestión financiera y contable</t>
+          <t>S2 Gestión de recursos humanos | S3 Gestión del abastecimiento | S5 Gestión financiera y contable</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -15334,11 +15334,19 @@
           <t>Oficina de Administración</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr"/>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Patricia Vivas</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Rosario Sonco / Marco Puente Arnao / Jose Silva / Brandy Zavala / Jenifer Cipra / Liseth Gomez / Mario Ganoza</t>
+        </is>
+      </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>AP101 SIGA MEF</t>
+          <t>AP057 Sistema Integrado de Gestión Administrativa</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -15352,14 +15360,10 @@
           <t>Media *</t>
         </is>
       </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>En baja/candidata. *</t>
-        </is>
-      </c>
+      <c r="AA116" t="inlineStr"/>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>De baja</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
@@ -15377,7 +15381,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BD SQL Server 2022 en producción; soporta AP101; dominio Gestión Administrativa, Personal y Logística *</t>
+          <t>BD SQL Server 2022 en producción; soporta AP057; dominio Gestión Administrativa, Personal y Logística *</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15453,7 +15457,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>S5 Gestión financiera y contable</t>
+          <t>S2 Gestión de recursos humanos | S3 Gestión del abastecimiento | S5 Gestión financiera y contable</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -15461,11 +15465,19 @@
           <t>Oficina de Administración</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Patricia Vivas</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Rosario Sonco / Marco Puente Arnao / Jose Silva / Brandy Zavala / Jenifer Cipra / Liseth Gomez / Mario Ganoza</t>
+        </is>
+      </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>AP101 SIGA MEF</t>
+          <t>AP057 Sistema Integrado de Gestión Administrativa</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -15482,7 +15494,7 @@
       <c r="AA117" t="inlineStr"/>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>Fuera de alcance</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
@@ -15500,7 +15512,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BD SQL Server 2008 R2 en producción; soporta AP101; dominio Gestión Administrativa, Personal y Logística *</t>
+          <t>BD SQL Server 2008 R2 en producción; soporta AP057; dominio Gestión Administrativa, Personal y Logística *</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15576,7 +15588,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>S5 Gestión financiera y contable</t>
+          <t>S2 Gestión de recursos humanos | S3 Gestión del abastecimiento | S5 Gestión financiera y contable</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -15584,11 +15596,19 @@
           <t>Oficina de Administración</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr"/>
-      <c r="V118" t="inlineStr"/>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Patricia Vivas</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Rosario Sonco / Marco Puente Arnao / Jose Silva / Brandy Zavala / Jenifer Cipra / Liseth Gomez / Mario Ganoza</t>
+        </is>
+      </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>AP101 SIGA MEF</t>
+          <t>AP057 Sistema Integrado de Gestión Administrativa</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -15604,12 +15624,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>Versión fuera de soporte. En baja/candidata. *</t>
+          <t>Versión fuera de soporte. *</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>De baja</t>
+          <t>Operativo</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
